--- a/CB_Payroll_English_Full.xlsx
+++ b/CB_Payroll_English_Full.xlsx
@@ -489,7 +489,7 @@
           <t>Bảng lương được xử lý vào ngày 25 hàng tháng.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Payroll is processed on the 25th of every month.</t>
         </is>
@@ -519,7 +519,7 @@
           <t>Chúng tôi tính lương dựa trên chấm công và bảng giờ làm việc.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>We calculate payroll based on attendance and timesheets.</t>
         </is>
@@ -549,7 +549,7 @@
           <t>Kỳ chạy lương bao gồm lương cơ bản, phụ cấp và các khoản khấu trừ.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>The payroll run includes salary, allowances, and deductions.</t>
         </is>
@@ -579,7 +579,7 @@
           <t>Nhân viên nhận phiếu lương qua email.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Employees receive their payslips by email.</t>
         </is>
@@ -609,7 +609,7 @@
           <t>Bảng lương tháng này đã được chốt.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>This month's payroll has been finalized.</t>
         </is>
@@ -639,7 +639,7 @@
           <t>Chúng tôi thực hiện tính lương cho hơn mười lăm công ty khách hàng mỗi tháng.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>We run payroll for more than fifteen client companies every month.</t>
         </is>
@@ -669,7 +669,7 @@
           <t>Chu kỳ tính lương bao gồm chấm công, tính lương và chi trả.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>The payroll cycle covers attendance, salary calculation, and payment.</t>
         </is>
@@ -699,9 +699,9 @@
           <t>Vui lòng kiểm tra báo cáo lương trước khi gửi cho khách hàng.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Please review the payroll report before we send it to the client.</t>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Please review the payroll report, before we send it to the client.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,7 +729,7 @@
           <t>Mọi thay đổi trong dữ liệu lương phải được xác nhận bằng văn bản.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Any changes to payroll data must be confirmed in writing.</t>
         </is>
@@ -759,7 +759,7 @@
           <t>Chúng tôi đối chiếu số liệu lương với bộ phận kế toán vào mỗi cuối tháng.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>We reconcile payroll figures with the accounting team every month end.</t>
         </is>
@@ -789,7 +789,7 @@
           <t>Để tôi giải thích cách chúng tôi tính lương cho công ty của anh/chị.</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Let me explain how we calculate the payroll for your company.</t>
         </is>
@@ -819,9 +819,9 @@
           <t>Tôi khuyến nghị chạy thử mô phỏng lương trước kỳ chính thức.</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>I recommend running a payroll simulation before the official cycle.</t>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>I recommend running a payroll simulation, before the official cycle.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -849,7 +849,7 @@
           <t>Dựa trên đánh giá của chúng tôi, quy trình tính lương có thể được đơn giản hóa.</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Based on our review, the payroll process could be simplified.</t>
         </is>
@@ -879,7 +879,7 @@
           <t>Tôi đề xuất tự động hóa quy trình phê duyệt lương.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>I would suggest automating the payroll approval workflow.</t>
         </is>
@@ -909,7 +909,7 @@
           <t>Hãy để chúng tôi trình bày với anh/chị lịch trình tính lương theo từng bước.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Let us walk you through the payroll timeline step by step.</t>
         </is>
@@ -939,7 +939,7 @@
           <t>Hãy chuyển sang mục lương trong chương trình họp.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Let's move on to the payroll agenda item.</t>
         </is>
@@ -969,7 +969,7 @@
           <t>Anh/chị có thể chia sẻ báo cáo lương lên màn hình được không?</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Could you share the payroll report on the screen, please?</t>
         </is>
@@ -999,7 +999,7 @@
           <t>Tôi muốn nêu một mối lo ngại về lịch trình lương tháng này.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>I'd like to raise a concern about this month's payroll timeline.</t>
         </is>
@@ -1029,7 +1029,7 @@
           <t>Tóm lại, lương sẽ được xử lý vào ngày hai mươi lăm như thường lệ.</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>To summarize, payroll will be processed by the twenty fifth as usual.</t>
         </is>
@@ -1059,9 +1059,9 @@
           <t>Có ai có câu hỏi nào về quy trình lương trước khi chúng ta kết thúc mục này không?</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Does anyone have questions about the payroll process before we close this item?</t>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Does anyone have questions about the payroll process, before we close this item?</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1089,7 +1089,7 @@
           <t>Thật ra, tôi nghĩ quy trình tính lương của chúng ta đã cải thiện rất nhiều trong năm nay.</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Honestly, I think our payroll process has improved a lot this year.</t>
         </is>
@@ -1119,7 +1119,7 @@
           <t>Nếu là khách hàng, tôi sẽ muốn báo cáo lương minh bạch hơn.</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>If I were the client, I'd want more transparency in the payroll report.</t>
         </is>
@@ -1149,7 +1149,7 @@
           <t>Theo kinh nghiệm của tôi, hầu hết vấn đề lương đến từ việc cập nhật dữ liệu trễ.</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>From my experience, most payroll issues come from late data updates.</t>
         </is>
@@ -1179,7 +1179,7 @@
           <t>Tôi tin rằng tự động hóa tính lương sẽ giúp tiết kiệm rất nhiều thời gian.</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>I believe automating payroll would save us a lot of time.</t>
         </is>
@@ -1209,7 +1209,7 @@
           <t>Điều tôi lo lắng nhất về lương là bị trễ hạn nộp.</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>What worries me most about payroll is missing a deadline.</t>
         </is>
@@ -1239,7 +1239,7 @@
           <t>Lương cơ bản của bạn là 15 triệu đồng mỗi tháng.</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Your basic salary is 15 million VND per month.</t>
         </is>
@@ -1269,7 +1269,7 @@
           <t>Lương được trả qua chuyển khoản ngân hàng.</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Salary is paid via bank transfer.</t>
         </is>
@@ -1299,7 +1299,7 @@
           <t>Chúng tôi xem xét lại lương mỗi năm một lần.</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>We review salaries once a year.</t>
         </is>
@@ -1329,7 +1329,7 @@
           <t>Việc tăng lương sẽ có hiệu lực từ tháng Một.</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>The salary increase will take effect from January.</t>
         </is>
@@ -1359,7 +1359,7 @@
           <t>Bạn có thể cho tôi biết mức lương mong muốn không?</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Can you tell me your expected salary?</t>
         </is>
@@ -1389,7 +1389,7 @@
           <t>Lương gộp bao gồm lương cơ bản cộng phụ cấp.</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>The gross salary includes basic salary plus allowances.</t>
         </is>
@@ -1419,7 +1419,7 @@
           <t>Lương thực nhận là số tiền nhân viên thực sự nhận được sau khi trừ các khoản.</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Net salary is what the employee actually receives after deductions.</t>
         </is>
@@ -1449,7 +1449,7 @@
           <t>Việc điều chỉnh lương phải tuân theo chính sách lương của công ty.</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Salary adjustments must follow the company's compensation policy.</t>
         </is>
@@ -1479,7 +1479,7 @@
           <t>Chúng tôi so sánh mức lương với thị trường mỗi năm.</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>We benchmark salaries against the market every year.</t>
         </is>
@@ -1509,7 +1509,7 @@
           <t>Cơ cấu lương có năm bậc chức danh công việc.</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>The salary structure has five job grades.</t>
         </is>
@@ -1539,7 +1539,7 @@
           <t>Tôi có thể giải thích chi tiết sự khác biệt giữa lương gộp và lương thực nhận.</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>I can explain the difference between gross and net salary in detail.</t>
         </is>
@@ -1569,7 +1569,7 @@
           <t>Chúng tôi khuyên nên rà soát cơ cấu lương mỗi năm một lần.</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>We advise reviewing the salary structure once a year.</t>
         </is>
@@ -1599,7 +1599,7 @@
           <t>Theo tôi, mức lương cho vị trí này khá cạnh tranh so với thị trường.</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>In my opinion, the salary range for this position is competitive.</t>
         </is>
@@ -1629,7 +1629,7 @@
           <t>Tôi đề xuất điều chỉnh lương dựa trên kết quả đánh giá hiệu suất.</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>I would recommend adjusting the salary based on performance review results.</t>
         </is>
@@ -1659,7 +1659,7 @@
           <t>Để tôi làm rõ cách áp dụng việc tăng lương.</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Let me clarify how the salary increase will be applied.</t>
         </is>
@@ -1689,7 +1689,7 @@
           <t>Hãy chuyển sang thảo luận về việc rà soát lương năm nay.</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Let's move on to discuss the salary review for this year.</t>
         </is>
@@ -1719,7 +1719,7 @@
           <t>Anh/chị có thể trình bày cơ cấu lương được đề xuất không?</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Could you walk us through the proposed salary structure?</t>
         </is>
@@ -1749,7 +1749,7 @@
           <t>Tôi muốn nêu một điểm về chênh lệch lương giữa các phòng ban.</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>I'd like to raise a point regarding the salary gap between departments.</t>
         </is>
@@ -1779,7 +1779,7 @@
           <t>Tóm lại, chúng ta đã thống nhất tăng ngân sách lương thêm mười phần trăm.</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>To summarize, we agreed to increase the salary budget by ten percent.</t>
         </is>
@@ -1809,7 +1809,7 @@
           <t>Hãy đặt lịch họp tiếp theo để chốt quyết định về lương.</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Let's set a follow up meeting to finalize the salary decision.</t>
         </is>
@@ -1839,7 +1839,7 @@
           <t>Thật ra, tôi nghĩ minh bạch về lương giúp xây dựng niềm tin hơn với nhân viên.</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Honestly, I think salary transparency builds more trust with employees.</t>
         </is>
@@ -1869,7 +1869,7 @@
           <t>Nếu đàm phán lương, tôi sẽ tập trung vào tổng gói thu nhập, không chỉ lương cơ bản.</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>If I were negotiating salary, I'd focus on the total package, not just the base.</t>
         </is>
@@ -1899,7 +1899,7 @@
           <t>Theo kinh nghiệm của tôi, khiếu nại về lương thường xuất phát từ việc truyền đạt không rõ ràng.</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>From my experience, salary complaints usually come from unclear communication.</t>
         </is>
@@ -1929,7 +1929,7 @@
           <t>Tôi tin rằng cơ cấu lương công bằng giúp giảm tỷ lệ nghỉ việc.</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>I believe fair salary structures reduce staff turnover.</t>
         </is>
@@ -1959,7 +1959,7 @@
           <t>Điều khiến tôi bất ngờ nhất là kỳ vọng về lương khác nhau rất nhiều theo từng khu vực.</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>What surprises me most is how much salary expectations vary by region.</t>
         </is>
@@ -1989,7 +1989,7 @@
           <t>Công ty cấp phụ cấp ăn trưa 730,000 đồng mỗi tháng.</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>The company provides a lunch allowance of 730,000 VND per month.</t>
         </is>
@@ -2019,7 +2019,7 @@
           <t>Phụ cấp đi lại được bao gồm trong gói lương của bạn.</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Transportation allowance is included in your salary package.</t>
         </is>
@@ -2049,7 +2049,7 @@
           <t>Khoản phụ cấp này không chịu thuế.</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>This allowance is not subject to tax.</t>
         </is>
@@ -2079,7 +2079,7 @@
           <t>Nhân viên đi công tác được nhận phụ cấp công tác.</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Employees on business trips receive a travel allowance.</t>
         </is>
@@ -2109,7 +2109,7 @@
           <t>Phụ cấp nhà ở tùy thuộc vào vị trí của bạn.</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Housing allowance depends on your position.</t>
         </is>
@@ -2139,7 +2139,7 @@
           <t>Chính sách phụ cấp bao gồm chi phí đi lại, ăn trưa và điện thoại.</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>The allowance policy covers transportation, meal, and phone expenses.</t>
         </is>
@@ -2169,7 +2169,7 @@
           <t>Một số khoản phụ cấp phải chịu thuế, một số khác được miễn thuế.</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Some allowances are taxable, while others are exempt.</t>
         </is>
@@ -2199,7 +2199,7 @@
           <t>Phụ cấp nhà ở được giới hạn ở một mức cố định mỗi tháng.</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>The housing allowance is capped at a fixed amount per month.</t>
         </is>
@@ -2229,7 +2229,7 @@
           <t>Chúng tôi cần chứng từ để chứng minh khoản phụ cấp.</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>We need supporting documents to justify the allowance.</t>
         </is>
@@ -2259,7 +2259,7 @@
           <t>Mức phụ cấp thay đổi tùy theo vị trí của nhân viên.</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Allowance rates vary depending on the employee's position.</t>
         </is>
@@ -2289,7 +2289,7 @@
           <t>Để tôi giải thích khoản phụ cấp nào phải chịu thuế thu nhập cá nhân.</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Let me explain which allowances are subject to personal income tax.</t>
         </is>
@@ -2319,7 +2319,7 @@
           <t>Tôi đề xuất chuẩn hóa chính sách phụ cấp giữa các phòng ban.</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>I suggest standardizing the allowance policy across departments.</t>
         </is>
@@ -2349,7 +2349,7 @@
           <t>Dựa trên kết quả kiểm toán, một số khoản phụ cấp cần chứng từ rõ ràng hơn.</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Based on the audit, some allowances need clearer documentation.</t>
         </is>
@@ -2379,7 +2379,7 @@
           <t>Chúng tôi khuyến nghị giới hạn phụ cấp đi lại ở mức hợp lý.</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>We recommend capping the travel allowance at a reasonable level.</t>
         </is>
@@ -2409,7 +2409,7 @@
           <t>Hãy để tôi trình bày cách tính từng khoản phụ cấp.</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Let me walk you through how each allowance is calculated.</t>
         </is>
@@ -2439,7 +2439,7 @@
           <t>Hãy chuyển sang rà soát chính sách phụ cấp.</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Let's move on to review the allowance policy.</t>
         </is>
@@ -2469,7 +2469,7 @@
           <t>Anh/chị có thể làm rõ những khoản phụ cấp nào nằm trong đề xuất này không?</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Could you clarify which allowances are included in this proposal?</t>
         </is>
@@ -2499,7 +2499,7 @@
           <t>Tôi muốn hỏi về khoản phụ cấp đi lại.</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>I'd like to raise a question about the transportation allowance.</t>
         </is>
@@ -2529,7 +2529,7 @@
           <t>Tóm lại, ngân sách phụ cấp sẽ không thay đổi trong quý này.</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>To summarize, the allowance budget will remain unchanged this quarter.</t>
         </is>
@@ -2559,9 +2559,9 @@
           <t>Hãy chốt danh sách phụ cấp trước khi kết thúc cuộc họp này.</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Let's finalize the allowance list before the end of this meeting.</t>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Let's finalize the allowance list, before the end of this meeting.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2589,7 +2589,7 @@
           <t>Thật ra, tôi nghĩ phụ cấp nên đơn giản và dễ hiểu.</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Honestly, I think allowances should be simple and easy to understand.</t>
         </is>
@@ -2619,7 +2619,7 @@
           <t>Nếu thiết kế chính sách, tôi sẽ gắn phụ cấp với chi phí thực tế.</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>If I were designing the policy, I'd link allowances to actual costs.</t>
         </is>
@@ -2649,7 +2649,7 @@
           <t>Theo kinh nghiệm của tôi, quy định thuế về phụ cấp khiến nhiều nhân viên bối rối.</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>From my experience, tax rules on allowances confuse many employees.</t>
         </is>
@@ -2679,7 +2679,7 @@
           <t>Tôi tin rằng chứng từ phụ cấp rõ ràng giúp tránh tranh chấp sau này.</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>I believe clear allowance documentation prevents future disputes.</t>
         </is>
@@ -2709,9 +2709,9 @@
           <t>Điều tôi trân trọng nhất là khi khách hàng hỏi trước thay vì mặc định phụ cấp phải chịu thuế.</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>What I appreciate most is when clients ask before assuming an allowance is taxable.</t>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>What I appreciate most is when clients ask, before assuming an allowance is taxable.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2739,7 +2739,7 @@
           <t>Bảo hiểm xã hội được khấu trừ từ lương gộp của bạn.</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Social insurance is deducted from your gross salary.</t>
         </is>
@@ -2769,7 +2769,7 @@
           <t>Chúng tôi khấu trừ 10.5% cho bảo hiểm xã hội, y tế và thất nghiệp.</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>We deduct 10.5% for social, health, and unemployment insurance.</t>
         </is>
@@ -2799,7 +2799,7 @@
           <t>Thuế thu nhập cá nhân được khấu trừ hàng tháng.</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Personal income tax is deducted monthly.</t>
         </is>
@@ -2829,7 +2829,7 @@
           <t>Có sai sót trong khoản khấu trừ trên phiếu lương của bạn.</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>There was a deduction error on your payslip.</t>
         </is>
@@ -2859,7 +2859,7 @@
           <t>Vui lòng kiểm tra kỹ các khoản khấu trừ của bạn.</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Please check your deductions carefully.</t>
         </is>
@@ -2889,7 +2889,7 @@
           <t>Các khoản khấu trừ bắt buộc gồm bảo hiểm xã hội và thuế thu nhập cá nhân.</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Mandatory deductions include social insurance and personal income tax.</t>
         </is>
@@ -2919,7 +2919,7 @@
           <t>Chúng tôi khấu trừ phí công đoàn trực tiếp từ lương của nhân viên.</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>We deduct union fees directly from the employee's salary.</t>
         </is>
@@ -2949,9 +2949,9 @@
           <t>Vui lòng kiểm tra lại các khoản khấu trừ trước khi chốt lương.</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Please double check the deduction amounts before finalizing payroll.</t>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Please double check the deduction amounts, before finalizing payroll.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -2979,7 +2979,7 @@
           <t>Bất kỳ khoản khấu trừ không được phép nào cũng phải được báo cáo ngay.</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Any unauthorized deduction must be reported immediately.</t>
         </is>
@@ -3009,7 +3009,7 @@
           <t>Tổng các khoản khấu trừ được liệt kê chi tiết trên phiếu lương.</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>The total deductions are itemized on the payslip.</t>
         </is>
@@ -3039,7 +3039,7 @@
           <t>Tôi có thể giải thích từng khoản khấu trừ trên phiếu lương.</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>I can explain each deduction listed on the payslip.</t>
         </is>
@@ -3069,7 +3069,7 @@
           <t>Chúng tôi khuyên nhân viên nên kiểm tra các khoản khấu trừ mỗi tháng.</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>We advise employees to check their deductions every month.</t>
         </is>
@@ -3099,7 +3099,7 @@
           <t>Theo tôi, quy trình khấu trừ nên minh bạch hơn.</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>In my view, the deduction process should be more transparent.</t>
         </is>
@@ -3129,7 +3129,7 @@
           <t>Tôi đề xuất gửi bảng tóm tắt khấu trừ cho nhân viên hàng tháng.</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>I recommend sending a deduction summary to employees monthly.</t>
         </is>
@@ -3159,7 +3159,7 @@
           <t>Để tôi làm rõ vì sao khoản khấu trừ này được áp dụng trong tháng này.</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Let me clarify why this deduction was applied this month.</t>
         </is>
@@ -3189,7 +3189,7 @@
           <t>Hãy chuyển sang chủ đề khấu trừ lương.</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Let's move on to the topic of payroll deductions.</t>
         </is>
@@ -3219,7 +3219,7 @@
           <t>Anh/chị có thể giải thích vì sao khoản khấu trừ này được thêm vào phiếu lương không?</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Could you explain why this deduction was added to the payslip?</t>
         </is>
@@ -3249,7 +3249,7 @@
           <t>Tôi muốn nêu một mối lo ngại về khoản khấu trừ ngoài dự kiến.</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>I'd like to raise a concern about an unexpected deduction.</t>
         </is>
@@ -3279,9 +3279,9 @@
           <t>Tóm lại, tất cả các khoản khấu trừ sẽ được rà soát trước kỳ lương tiếp theo.</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>To summarize, all deductions will be reviewed before the next payroll run.</t>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>To summarize, all deductions will be reviewed, before the next payroll run.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3309,9 +3309,9 @@
           <t>Hãy thống nhất chính sách khấu trừ trước khi chuyển sang mục tiếp theo.</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Let's agree on the deduction policy before moving to the next item.</t>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Let's agree on the deduction policy, before moving to the next item.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3339,7 +3339,7 @@
           <t>Thật ra, tôi nghĩ chi tiết khấu trừ nên luôn được giải thích rõ trên phiếu lương.</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Honestly, I think deduction details should always be explained clearly on the payslip.</t>
         </is>
@@ -3369,7 +3369,7 @@
           <t>Nếu thấy một khoản khấu trừ bất thường, tôi sẽ kiểm tra lại ngay.</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>If I noticed an unusual deduction, I'd double check it right away.</t>
         </is>
@@ -3399,7 +3399,7 @@
           <t>Theo kinh nghiệm của tôi, hầu hết tranh chấp về khấu trừ chỉ là hiểu lầm đơn giản.</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>From my experience, most deduction disputes are simple misunderstandings.</t>
         </is>
@@ -3429,7 +3429,7 @@
           <t>Tôi tin rằng minh bạch về khấu trừ giúp giảm khiếu nại của nhân viên.</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>I believe transparency about deductions reduces employee complaints.</t>
         </is>
@@ -3459,9 +3459,9 @@
           <t>Điều quan trọng nhất với tôi là giải thích khấu trừ trước khi nhân viên hỏi.</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>What matters most to me is explaining deductions before employees ask.</t>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>What matters most to me is explaining deductions, before employees ask.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3489,7 +3489,7 @@
           <t>Lương làm thêm giờ bằng 150% mức lương giờ bình thường của bạn.</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Overtime pay is 150% of your normal hourly rate.</t>
         </is>
@@ -3519,9 +3519,9 @@
           <t>Bạn cần được phê duyệt trước khi làm thêm giờ.</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>You need approval before working overtime.</t>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>You need approval, before working overtime.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -3549,7 +3549,7 @@
           <t>Làm thêm giờ vào cuối tuần được trả 200%.</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Overtime on weekends is paid at 200%.</t>
         </is>
@@ -3579,7 +3579,7 @@
           <t>Vui lòng gửi yêu cầu làm thêm giờ trước thứ Sáu.</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Please submit your overtime request by Friday.</t>
         </is>
@@ -3609,7 +3609,7 @@
           <t>Bạn đã làm thêm bao nhiêu giờ trong tháng này?</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>How many overtime hours did you work this month?</t>
         </is>
@@ -3639,7 +3639,7 @@
           <t>Giờ làm thêm phải được quản lý trực tiếp phê duyệt trước.</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Overtime hours must be approved by the direct manager in advance.</t>
         </is>
@@ -3669,7 +3669,7 @@
           <t>Mức lương làm thêm vào ngày lễ là ba trăm phần trăm.</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>The overtime rate on public holidays is three hundred percent.</t>
         </is>
@@ -3699,7 +3699,7 @@
           <t>Chúng tôi theo dõi giờ làm thêm qua hệ thống chấm công.</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>We track overtime through the timekeeping system.</t>
         </is>
@@ -3729,7 +3729,7 @@
           <t>Làm thêm giờ quá mức có thể vi phạm quy định lao động.</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Excessive overtime may violate labor regulations.</t>
         </is>
@@ -3759,7 +3759,7 @@
           <t>Lương làm thêm được tính dựa trên đơn giá theo giờ.</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Overtime pay is calculated based on the hourly wage.</t>
         </is>
@@ -3789,7 +3789,7 @@
           <t>Tôi có thể giải thích cách xác định mức lương làm thêm giờ.</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>I can explain how the overtime rate is determined.</t>
         </is>
@@ -3819,7 +3819,7 @@
           <t>Chúng tôi khuyến nghị hạn chế làm thêm giờ để tránh rủi ro tuân thủ.</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>We recommend limiting overtime to avoid compliance risks.</t>
         </is>
@@ -3849,7 +3849,7 @@
           <t>Dựa trên số liệu, chi phí làm thêm giờ đã tăng trong quý này.</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Based on the data, overtime costs have increased this quarter.</t>
         </is>
@@ -3879,7 +3879,7 @@
           <t>Tôi đề xuất rà soát lại quy trình phê duyệt làm thêm giờ.</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>I suggest reviewing the overtime approval process.</t>
         </is>
@@ -3909,7 +3909,7 @@
           <t>Để tôi giải thích giới hạn pháp lý về số giờ làm thêm.</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Let me explain the legal limit on overtime hours.</t>
         </is>
@@ -3939,7 +3939,7 @@
           <t>Hãy chuyển sang thảo luận về tình hình làm thêm giờ tháng này.</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Let's move on to discuss the overtime situation this month.</t>
         </is>
@@ -3969,7 +3969,7 @@
           <t>Anh/chị có thể chia sẻ số liệu làm thêm giờ của bộ phận sản xuất không?</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Could you share the overtime data for the production team?</t>
         </is>
@@ -3999,7 +3999,7 @@
           <t>Tôi muốn nêu mối lo ngại về chi phí làm thêm giờ đang tăng.</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>I'd like to raise a concern about the rising overtime costs.</t>
         </is>
@@ -4029,7 +4029,7 @@
           <t>Tóm lại, yêu cầu làm thêm giờ phải được duyệt trước thứ Sáu.</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>To summarize, overtime requests must be approved before Friday.</t>
         </is>
@@ -4059,7 +4059,7 @@
           <t>Hãy đặt ra giới hạn cho số giờ làm thêm sắp tới.</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Let's set a limit on overtime hours going forward.</t>
         </is>
@@ -4089,7 +4089,7 @@
           <t>Thật ra, tôi nghĩ làm thêm giờ nên là tự nguyện, không nên ép buộc.</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Honestly, I think overtime should always be voluntary, not forced.</t>
         </is>
@@ -4119,7 +4119,7 @@
           <t>Nếu làm thêm giờ cứ tăng mãi, tôi sẽ nêu vấn đề này với ban quản lý.</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>If overtime kept increasing, I'd raise the issue with management.</t>
         </is>
@@ -4149,7 +4149,7 @@
           <t>Theo kinh nghiệm của tôi, chính sách làm thêm giờ không rõ ràng dẫn đến tranh chấp.</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>From my experience, unclear overtime policies lead to disputes.</t>
         </is>
@@ -4179,7 +4179,7 @@
           <t>Tôi tin rằng giới hạn làm thêm giờ hợp lý giúp bảo vệ sức khỏe nhân viên.</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>I believe reasonable overtime limits protect employee well-being.</t>
         </is>
@@ -4209,7 +4209,7 @@
           <t>Điều khiến tôi lo ngại nhất là làm thêm giờ trở thành chuyện bình thường thay vì ngoại lệ.</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>What concerns me most is overtime becoming the norm instead of the exception.</t>
         </is>
@@ -4239,7 +4239,7 @@
           <t>Giờ làm việc tiêu chuẩn là từ 8 giờ sáng đến 5 giờ chiều.</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Standard working hours are from 8 AM to 5 PM.</t>
         </is>
@@ -4269,7 +4269,7 @@
           <t>Chúng tôi làm việc 8 tiếng mỗi ngày, 5 ngày mỗi tuần.</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>We work 8 hours a day, 5 days a week.</t>
         </is>
@@ -4299,7 +4299,7 @@
           <t>Vui lòng chấm công vào và ra mỗi ngày.</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Please clock in and out every day.</t>
         </is>
@@ -4329,7 +4329,7 @@
           <t>Một số vị trí được áp dụng giờ làm việc linh hoạt.</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Flexible working hours are available for some positions.</t>
         </is>
@@ -4359,7 +4359,7 @@
           <t>Bạn bắt đầu làm việc lúc mấy giờ?</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>What time do you start work?</t>
         </is>
@@ -4389,7 +4389,7 @@
           <t>Giờ làm việc tiêu chuẩn là tám giờ mỗi ngày, năm ngày mỗi tuần.</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Standard working hours are eight hours per day, five days a week.</t>
         </is>
@@ -4419,7 +4419,7 @@
           <t>Nhân viên phải chấm công vào ra bằng máy quét vân tay.</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Employees must clock in and out using the fingerprint scanner.</t>
         </is>
@@ -4449,7 +4449,7 @@
           <t>Giờ làm việc linh hoạt áp dụng cho một số phòng ban.</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Flexible working hours apply to certain departments.</t>
         </is>
@@ -4479,7 +4479,7 @@
           <t>Chúng tôi theo dõi giờ làm việc để đảm bảo tuân thủ pháp luật.</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>We monitor working hours to ensure compliance with the law.</t>
         </is>
@@ -4509,7 +4509,7 @@
           <t>Việc đi trễ được ghi nhận tự động trong hệ thống.</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Late arrivals are recorded automatically in the system.</t>
         </is>
@@ -4539,7 +4539,7 @@
           <t>Tôi có thể giải thích chính sách giờ làm việc mà chúng tôi đề xuất.</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>I can explain our recommended working hours policy.</t>
         </is>
@@ -4569,7 +4569,7 @@
           <t>Chúng tôi khuyên nên áp dụng giờ làm việc linh hoạt khi có thể.</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>We advise adopting flexible working hours where possible.</t>
         </is>
@@ -4599,7 +4599,7 @@
           <t>Theo tôi, lịch làm việc theo ca hiện tại cần được điều chỉnh.</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>In my opinion, the current shift schedule needs adjustment.</t>
         </is>
@@ -4629,7 +4629,7 @@
           <t>Tôi đề xuất theo dõi giờ làm việc qua hệ thống điện tử.</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>I recommend tracking working hours through a digital system.</t>
         </is>
@@ -4659,7 +4659,7 @@
           <t>Để tôi làm rõ cách tính thời gian nghỉ giải lao trong giờ làm việc.</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Let me clarify how break time is counted in working hours.</t>
         </is>
@@ -4689,7 +4689,7 @@
           <t>Hãy chuyển sang phần cập nhật chính sách giờ làm việc.</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Let's move on to the working hours policy update.</t>
         </is>
@@ -4719,7 +4719,7 @@
           <t>Anh/chị có thể giải thích cách sắp xếp giờ làm việc linh hoạt mới không?</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Could you explain the new flexible working hours arrangement?</t>
         </is>
@@ -4749,7 +4749,7 @@
           <t>Tôi muốn hỏi về khung giờ làm việc cố định.</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>I'd like to raise a question about core working hours.</t>
         </is>
@@ -4779,7 +4779,7 @@
           <t>Tóm lại, chính sách giờ làm việc mới có hiệu lực từ tháng sau.</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>To summarize, the new working hours policy takes effect next month.</t>
         </is>
@@ -4809,9 +4809,9 @@
           <t>Hãy xác nhận mọi người đã hiểu lịch làm việc mới trước khi kết thúc.</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Let's confirm everyone understands the updated schedule before we close.</t>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Let's confirm everyone understands the updated schedule, before we close.</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -4839,7 +4839,7 @@
           <t>Thật ra, tôi nghĩ giờ làm việc linh hoạt giúp cải thiện sự hài lòng của nhân viên.</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Honestly, I think flexible working hours improve employee satisfaction.</t>
         </is>
@@ -4869,7 +4869,7 @@
           <t>Nếu quản lý một đội nhóm, tôi sẽ tập trung vào kết quả hơn là giờ giấc cứng nhắc.</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>If I managed a team, I'd focus on results rather than strict hours.</t>
         </is>
@@ -4899,7 +4899,7 @@
           <t>Theo kinh nghiệm của tôi, giờ làm việc cứng nhắc không phải lúc nào cũng tăng năng suất.</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>From my experience, rigid working hours don't always increase productivity.</t>
         </is>
@@ -4929,7 +4929,7 @@
           <t>Tôi tin rằng chính sách giờ làm việc rõ ràng giúp tránh nhầm lẫn về sau.</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>I believe a clear working hours policy avoids confusion later.</t>
         </is>
@@ -4959,7 +4959,7 @@
           <t>Điều tôi rút ra được là sự tin tưởng quan trọng hơn việc giám sát từng phút.</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>What I've learned is that trust matters more than monitoring every minute.</t>
         </is>
@@ -4989,7 +4989,7 @@
           <t>Mức đóng bảo hiểm xã hội được tính dựa trên lương của bạn.</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Social insurance contributions are based on your salary.</t>
         </is>
@@ -5019,7 +5019,7 @@
           <t>Công ty đóng 17.5% cho bảo hiểm xã hội.</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>The company pays 17.5% for social insurance.</t>
         </is>
@@ -5049,7 +5049,7 @@
           <t>Nhân viên đóng góp 8% lương của mình.</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Employees contribute 8% of their salary.</t>
         </is>
@@ -5079,7 +5079,7 @@
           <t>Bạn cần sổ bảo hiểm xã hội để hưởng các chế độ.</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>You need a social insurance book to claim benefits.</t>
         </is>
@@ -5109,7 +5109,7 @@
           <t>Bảo hiểm xã hội bao gồm chế độ ốm đau, thai sản và hưu trí.</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Social insurance covers sickness, maternity, and retirement.</t>
         </is>
@@ -5139,7 +5139,7 @@
           <t>Đóng bảo hiểm xã hội được chia sẻ giữa người sử dụng lao động và người lao động.</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Social insurance contributions are shared between employer and employee.</t>
         </is>
@@ -5169,7 +5169,7 @@
           <t>Chúng tôi nộp báo cáo bảo hiểm xã hội cho cơ quan chức năng mỗi tháng.</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>We submit the social insurance report to the authority every month.</t>
         </is>
@@ -5199,7 +5199,7 @@
           <t>Nhân viên mới phải được đăng ký bảo hiểm xã hội trong thời hạn quy định.</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>New employees must be registered for social insurance within the required time frame.</t>
         </is>
@@ -5229,7 +5229,7 @@
           <t>Sổ bảo hiểm xã hội ghi lại quá trình đóng bảo hiểm của nhân viên.</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>The social insurance book records the employee's contribution history.</t>
         </is>
@@ -5259,9 +5259,9 @@
           <t>Vui lòng cập nhật tình trạng bảo hiểm xã hội khi nhân viên nghỉ việc.</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Please update the social insurance status when an employee resigns.</t>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Please update the social insurance status, when an employee resigns.</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -5289,7 +5289,7 @@
           <t>Tôi có thể giải thích tỷ lệ đóng bảo hiểm xã hội trong năm nay.</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>I can explain the social insurance contribution rates for this year.</t>
         </is>
@@ -5319,7 +5319,7 @@
           <t>Chúng tôi khuyên nên đăng ký bảo hiểm cho nhân viên mới càng sớm càng tốt.</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>We advise registering new employees as soon as possible.</t>
         </is>
@@ -5349,7 +5349,7 @@
           <t>Dựa trên kinh nghiệm của chúng tôi, đăng ký trễ thường dẫn đến bị phạt.</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Based on our experience, late registration often causes penalties.</t>
         </is>
@@ -5379,7 +5379,7 @@
           <t>Tôi đề xuất cập nhật hồ sơ bảo hiểm xã hội hàng tháng.</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>I recommend keeping social insurance records updated monthly.</t>
         </is>
@@ -5409,7 +5409,7 @@
           <t>Để tôi giải thích các quyền lợi nhân viên nhận được từ bảo hiểm xã hội.</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Let me explain the benefits employees receive from social insurance.</t>
         </is>
@@ -5439,7 +5439,7 @@
           <t>Hãy chuyển sang phần cập nhật tuân thủ bảo hiểm xã hội.</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Let's move on to the social insurance compliance update.</t>
         </is>
@@ -5469,7 +5469,7 @@
           <t>Anh/chị có thể chia sẻ những thay đổi mới nhất về quy định bảo hiểm xã hội không?</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Could you share the latest social insurance regulation changes?</t>
         </is>
@@ -5499,7 +5499,7 @@
           <t>Tôi muốn nêu mối lo ngại về việc đăng ký bảo hiểm xã hội bị chậm trễ.</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>I'd like to raise a concern about a delayed social insurance registration.</t>
         </is>
@@ -5529,7 +5529,7 @@
           <t>Tóm lại, tất cả nhân viên mới sẽ được đăng ký trước thứ Sáu này.</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>To summarize, all new employees will be registered by this Friday.</t>
         </is>
@@ -5559,9 +5559,9 @@
           <t>Hãy xác nhận các việc cần làm về bảo hiểm xã hội trước khi kết thúc.</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Let's confirm the action items for social insurance before we finish.</t>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Let's confirm the action items for social insurance, before we finish.</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -5589,7 +5589,7 @@
           <t>Thật ra, tôi nghĩ bảo hiểm xã hội bảo vệ người lao động nhiều hơn mọi người nghĩ.</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Honestly, I think social insurance protects employees more than people realize.</t>
         </is>
@@ -5619,7 +5619,7 @@
           <t>Nếu việc đăng ký bị chậm trễ, tôi sẽ báo cáo lên ngay lập tức.</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>If registration was delayed, I'd escalate it immediately.</t>
         </is>
@@ -5649,7 +5649,7 @@
           <t>Theo kinh nghiệm của tôi, nhân viên thường đánh giá thấp quyền lợi bảo hiểm xã hội.</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>From my experience, employees often underestimate social insurance benefits.</t>
         </is>
@@ -5679,7 +5679,7 @@
           <t>Tôi tin rằng hồ sơ đóng bảo hiểm chính xác giúp tránh tranh chấp sau này.</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>I believe accurate contribution records prevent future disputes.</t>
         </is>
@@ -5709,7 +5709,7 @@
           <t>Điều tôi lo lắng nhất là sai sót trong quá trình đóng bảo hiểm của ai đó.</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>What worries me most is a mistake in someone's social insurance history.</t>
         </is>
@@ -5739,7 +5739,7 @@
           <t>Thuế thu nhập cá nhân được tính dựa trên thu nhập chịu thuế của bạn.</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Personal income tax is calculated based on your taxable income.</t>
         </is>
@@ -5769,7 +5769,7 @@
           <t>Mức thuế phụ thuộc vào bậc thu nhập của bạn.</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>The tax rate depends on your income bracket.</t>
         </is>
@@ -5799,7 +5799,7 @@
           <t>Bạn có thể đăng ký giảm trừ gia cảnh để giảm thuế.</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>You can register for family deductions to reduce tax.</t>
         </is>
@@ -5829,9 +5829,9 @@
           <t>Thuế TNCN được khấu trừ trước khi bạn nhận lương.</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>PIT is deducted before you receive your salary.</t>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>PIT is deducted, before you receive your salary.</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -5859,7 +5859,7 @@
           <t>Bạn có người phụ thuộc để giảm trừ thuế không?</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>Do you have any dependents for tax deduction?</t>
         </is>
@@ -5889,7 +5889,7 @@
           <t>Thuế thu nhập cá nhân được khấu trừ hàng tháng theo biểu thuế lũy tiến.</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>Personal income tax is withheld monthly based on the progressive tax table.</t>
         </is>
@@ -5919,7 +5919,7 @@
           <t>Nhân viên có thể đăng ký người phụ thuộc để giảm thu nhập chịu thuế.</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>Employees can register dependents to reduce their taxable income.</t>
         </is>
@@ -5949,7 +5949,7 @@
           <t>Chúng tôi cấp chứng từ khấu trừ thuế khi có yêu cầu.</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>We issue the tax withholding certificate upon request.</t>
         </is>
@@ -5979,9 +5979,9 @@
           <t>Mã số thuế phải được đăng ký trước kỳ tính lương đầu tiên.</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>The tax code must be registered before the first payroll cycle.</t>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>The tax code must be registered, before the first payroll cycle.</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6009,7 +6009,7 @@
           <t>Nhân viên không cư trú bị đánh thuế theo mức cố định.</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>Non-resident employees are taxed at a flat rate.</t>
         </is>
@@ -6039,7 +6039,7 @@
           <t>Tôi có thể giải thích cách tính thuế thu nhập cá nhân cho nhân viên nước ngoài.</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>I can explain how personal income tax is calculated for foreign employees.</t>
         </is>
@@ -6069,7 +6069,7 @@
           <t>Chúng tôi khuyên nên đăng ký người phụ thuộc sớm để giảm thu nhập chịu thuế.</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>We advise registering dependents early to reduce taxable income.</t>
         </is>
@@ -6099,7 +6099,7 @@
           <t>Theo tôi, trường hợp này cần tham vấn với cơ quan thuế.</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>In my opinion, this case requires consultation with the tax authority.</t>
         </is>
@@ -6129,7 +6129,7 @@
           <t>Tôi đề xuất rà soát bậc thuế của anh/chị mỗi năm.</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>I recommend reviewing your tax bracket every year.</t>
         </is>
@@ -6159,7 +6159,7 @@
           <t>Để tôi làm rõ sự khác biệt giữa thuế suất cư trú và không cư trú.</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>Let me clarify the difference between resident and non-resident tax rates.</t>
         </is>
@@ -6189,7 +6189,7 @@
           <t>Hãy chuyển sang thảo luận về thuế thu nhập cá nhân.</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>Let's move on to the personal income tax discussion.</t>
         </is>
@@ -6219,7 +6219,7 @@
           <t>Anh/chị có thể làm rõ quy định thuế mới ảnh hưởng thế nào đến khách hàng của chúng ta không?</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>Could you clarify how the new tax regulation affects our clients?</t>
         </is>
@@ -6249,7 +6249,7 @@
           <t>Tôi muốn hỏi về cách tính thuế cho người lao động nước ngoài.</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>I'd like to raise a question about tax calculation for expatriates.</t>
         </is>
@@ -6279,7 +6279,7 @@
           <t>Tóm lại, chúng ta sẽ cập nhật mẫu tính thuế trong tuần này.</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>To summarize, we will update the tax calculation template this week.</t>
         </is>
@@ -6309,7 +6309,7 @@
           <t>Hãy thống nhất các bước tiếp theo cho vấn đề thuế thu nhập cá nhân.</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>Let's agree on next steps for the personal income tax matter.</t>
         </is>
@@ -6339,7 +6339,7 @@
           <t>Thật ra, tôi nghĩ quy định thuế thu nhập cá nhân có thể gây nhầm lẫn ngay cả với người trong nghề.</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>Honestly, I think personal income tax rules can be confusing even for professionals.</t>
         </is>
@@ -6369,7 +6369,7 @@
           <t>Nếu khách hàng hiểu sai thuế suất, tôi sẽ kiên nhẫn giải thích kèm ví dụ.</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>If a client misunderstood the tax rate, I'd explain it patiently with examples.</t>
         </is>
@@ -6399,7 +6399,7 @@
           <t>Theo kinh nghiệm của tôi, việc đăng ký người phụ thuộc thường bị bỏ sót.</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>From my experience, dependent registration is often overlooked.</t>
         </is>
@@ -6429,7 +6429,7 @@
           <t>Tôi tin rằng hướng dẫn thuế rõ ràng giúp nhân viên bớt căng thẳng rất nhiều.</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>I believe clear tax guidance saves employees a lot of stress.</t>
         </is>
@@ -6459,7 +6459,7 @@
           <t>Điều tôi thấy khó nhất là giải thích các bậc thuế một cách đơn giản.</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>What I find most challenging is explaining tax brackets simply.</t>
         </is>
@@ -6489,7 +6489,7 @@
           <t>Quyết toán thuế TNCN phải hoàn thành trước ngày 31 tháng 3.</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>PIT finalization must be completed by March 31st.</t>
         </is>
@@ -6519,7 +6519,7 @@
           <t>Chúng tôi cần quyết toán thuế TNCN của bạn cho năm trước.</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>We need to finalize your personal income tax for last year.</t>
         </is>
@@ -6549,7 +6549,7 @@
           <t>Bạn có thể nhận được tiền hoàn thuế sau khi quyết toán.</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>You may receive a tax refund after finalization.</t>
         </is>
@@ -6579,7 +6579,7 @@
           <t>Vui lòng cung cấp hồ sơ đăng ký người phụ thuộc.</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>Please provide your dependent registration documents.</t>
         </is>
@@ -6609,7 +6609,7 @@
           <t>Hạn chót quyết toán thuế đang đến gần.</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>The finalization deadline is approaching.</t>
         </is>
@@ -6639,7 +6639,7 @@
           <t>Quyết toán thuế thu nhập cá nhân phải hoàn tất trước cuối tháng ba.</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>PIT finalization must be completed by the end of March.</t>
         </is>
@@ -6669,7 +6669,7 @@
           <t>Chúng tôi chuẩn bị hồ sơ quyết toán cho từng nhân viên được ủy quyền.</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>We prepare the finalization file for each authorized employee.</t>
         </is>
@@ -6699,9 +6699,9 @@
           <t>Khoản hoàn thuế sẽ được xử lý sau khi quyết toán được duyệt.</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>Any tax refund will be processed after the finalization is approved.</t>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>Any tax refund will be processed, after the finalization is approved.</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -6729,7 +6729,7 @@
           <t>Nhân viên có thu nhập từ nhiều nguồn phải tự quyết toán thuế.</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>Employees with income from multiple sources must self-finalize their tax.</t>
         </is>
@@ -6759,7 +6759,7 @@
           <t>Chúng tôi kiểm tra chéo dữ liệu quyết toán với các báo cáo thuế hàng tháng.</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>We double check the finalization data against the monthly tax reports.</t>
         </is>
@@ -6789,7 +6789,7 @@
           <t>Tôi có thể giải thích quy trình quyết toán thuế thu nhập cá nhân theo từng bước.</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>I can explain the PIT finalization process step by step.</t>
         </is>
@@ -6819,7 +6819,7 @@
           <t>Chúng tôi khuyên nên chuẩn bị hồ sơ quyết toán sớm để tránh dồn việc.</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>We advise preparing finalization documents early to avoid the rush.</t>
         </is>
@@ -6849,7 +6849,7 @@
           <t>Dựa trên kết quả rà soát, anh/chị có thể được hoàn thuế.</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>Based on the review, you may be eligible for a tax refund.</t>
         </is>
@@ -6879,7 +6879,7 @@
           <t>Tôi đề xuất ủy quyền cho công ty quyết toán thuế thay cho anh/chị.</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>I recommend authorizing the company to finalize your tax on your behalf.</t>
         </is>
@@ -6909,7 +6909,7 @@
           <t>Để tôi làm rõ ai là người phải tự quyết toán thuế thu nhập cá nhân.</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>Let me clarify who is required to self-finalize their personal income tax.</t>
         </is>
@@ -6939,7 +6939,7 @@
           <t>Hãy chuyển sang lịch trình quyết toán thuế thu nhập cá nhân.</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>Let's move on to the PIT finalization timeline.</t>
         </is>
@@ -6969,7 +6969,7 @@
           <t>Anh/chị có thể chia sẻ tiến độ quyết toán của các khách hàng lớn không?</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>Could you share the finalization progress for our major clients?</t>
         </is>
@@ -6999,7 +6999,7 @@
           <t>Tôi muốn nêu mối lo ngại về việc thiếu hồ sơ quyết toán.</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>I'd like to raise a concern about missing finalization documents.</t>
         </is>
@@ -7029,7 +7029,7 @@
           <t>Tóm lại, tất cả hồ sơ quyết toán phải sẵn sàng trước tháng ba.</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>To summarize, all finalization files must be ready before March.</t>
         </is>
@@ -7059,7 +7059,7 @@
           <t>Hãy phân công trách nhiệm cho hồ sơ quyết toán của từng khách hàng.</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>Let's assign responsibility for each client's finalization file.</t>
         </is>
@@ -7089,7 +7089,7 @@
           <t>Thật ra, tôi nghĩ mùa quyết toán thuế thu nhập cá nhân là thời điểm bận rộn nhất trong năm của chúng tôi.</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>Honestly, I think PIT finalization season is the busiest time of our year.</t>
         </is>
@@ -7119,7 +7119,7 @@
           <t>Nếu thiếu hồ sơ, tôi sẽ liên hệ với khách hàng ngay.</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>If documents were missing, I'd follow up with the client right away.</t>
         </is>
@@ -7149,7 +7149,7 @@
           <t>Theo kinh nghiệm của tôi, chuẩn bị sớm giúp việc quyết toán suôn sẻ hơn nhiều.</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>From my experience, early preparation makes finalization much smoother.</t>
         </is>
@@ -7179,9 +7179,9 @@
           <t>Tôi tin rằng khách hàng đánh giá cao việc được nhắc nhở trước hạn quyết toán.</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>I believe clients appreciate reminders before the finalization deadline.</t>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>I believe clients appreciate reminders, before the finalization deadline.</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -7209,7 +7209,7 @@
           <t>Điều tôi thích nhất là giúp khách hàng nhận được tiền hoàn thuế một cách suôn sẻ.</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>What I enjoy most is helping clients get their tax refund smoothly.</t>
         </is>
@@ -7239,7 +7239,7 @@
           <t>Hợp đồng lao động của bạn có thời hạn 12 tháng.</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>Your labor contract is for 12 months.</t>
         </is>
@@ -7269,9 +7269,9 @@
           <t>Vui lòng ký hợp đồng lao động trước ngày bắt đầu làm việc.</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>Please sign the labor contract before your start date.</t>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>Please sign the labor contract, before your start date.</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -7299,7 +7299,7 @@
           <t>Hợp đồng bao gồm lương, vị trí và điều kiện làm việc.</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>The contract includes salary, position, and working conditions.</t>
         </is>
@@ -7329,7 +7329,7 @@
           <t>Chúng tôi cần gia hạn hợp đồng lao động của bạn vào tháng sau.</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>We need to renew your labor contract next month.</t>
         </is>
@@ -7359,9 +7359,9 @@
           <t>Cả hai bên phải đồng ý trước khi chấm dứt hợp đồng.</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>Both parties must agree before terminating the contract.</t>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>Both parties must agree, before terminating the contract.</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -7389,7 +7389,7 @@
           <t>Hợp đồng lao động quy định vị trí công việc, lương và các phúc lợi.</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>The labor contract specifies the job position, salary, and benefits.</t>
         </is>
@@ -7419,9 +7419,9 @@
           <t>Chúng tôi phải gia hạn hợp đồng lao động trước khi hết hạn.</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>We must renew the labor contract before it expires.</t>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>We must renew the labor contract, before it expires.</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -7449,7 +7449,7 @@
           <t>Thời gian thử việc không được vượt quá sáu mươi ngày cho vị trí này.</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>A probation period cannot exceed sixty days for this position.</t>
         </is>
@@ -7479,9 +7479,9 @@
           <t>Hai bên phải ký hợp đồng lao động trước khi nhân viên bắt đầu làm việc.</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>Both parties must sign the labor contract before the employee starts work.</t>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>Both parties must sign the labor contract, before the employee starts work.</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -7509,7 +7509,7 @@
           <t>Việc chấm dứt hợp đồng cần thông báo trước theo đúng quy định pháp luật.</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>Contract termination requires proper notice according to the law.</t>
         </is>
@@ -7539,7 +7539,7 @@
           <t>Tôi có thể giải thích các điều khoản chính cần có trong hợp đồng lao động.</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>I can explain the key terms that should be included in a labor contract.</t>
         </is>
@@ -7569,7 +7569,7 @@
           <t>Chúng tôi khuyên nên gia hạn hợp đồng ít nhất ba mươi ngày trước khi hết hạn.</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>We advise renewing contracts at least thirty days before expiration.</t>
         </is>
@@ -7599,7 +7599,7 @@
           <t>Theo tôi, điều khoản thử việc cần được quy định rõ ràng.</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>In my opinion, the probation terms should be clearly defined.</t>
         </is>
@@ -7629,7 +7629,7 @@
           <t>Tôi đề xuất rà soát mẫu hợp đồng cùng với bộ phận pháp lý.</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>I recommend reviewing the contract template with the legal team.</t>
         </is>
@@ -7659,7 +7659,7 @@
           <t>Để tôi làm rõ thời gian báo trước cần thiết khi chấm dứt hợp đồng.</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>Let me clarify the notice period required for contract termination.</t>
         </is>
@@ -7689,7 +7689,7 @@
           <t>Hãy chuyển sang rà soát các hợp đồng lao động sắp gia hạn.</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>Let's move on to review upcoming labor contract renewals.</t>
         </is>
@@ -7719,7 +7719,7 @@
           <t>Anh/chị có thể chia sẻ danh sách hợp đồng hết hạn trong quý này không?</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>Could you share the list of contracts expiring this quarter?</t>
         </is>
@@ -7749,7 +7749,7 @@
           <t>Tôi muốn hỏi về mẫu hợp đồng mới.</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>I'd like to raise a question about the new contract template.</t>
         </is>
@@ -7779,9 +7779,9 @@
           <t>Tóm lại, tất cả các hợp đồng sẽ được gia hạn trước ngày hết hạn.</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>To summarize, all renewals will be completed before the expiration date.</t>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>To summarize, all renewals will be completed, before the expiration date.</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -7809,7 +7809,7 @@
           <t>Hãy xác nhận ai sẽ theo dõi việc này với từng khách hàng.</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>Let's confirm who will follow up with each client on this.</t>
         </is>
@@ -7839,7 +7839,7 @@
           <t>Thật ra, tôi nghĩ hợp đồng lao động rõ ràng giúp tránh hầu hết các tranh chấp sau này.</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>Honestly, I think a clear labor contract prevents most future disputes.</t>
         </is>
@@ -7869,7 +7869,7 @@
           <t>Nếu hợp đồng sắp hết hạn, tôi sẽ nhắc khách hàng sớm.</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>If a contract was about to expire, I'd remind the client early.</t>
         </is>
@@ -7899,7 +7899,7 @@
           <t>Theo kinh nghiệm của tôi, điều khoản thử việc thường bị nhân viên mới hiểu sai.</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>From my experience, probation terms are often misunderstood by new employees.</t>
         </is>
@@ -7929,7 +7929,7 @@
           <t>Tôi tin rằng mọi hợp đồng nên được bộ phận pháp lý rà soát trước khi ký.</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>I believe every contract should be reviewed by legal before signing.</t>
         </is>
@@ -7959,7 +7959,7 @@
           <t>Điều tôi rút ra được là điều khoản chấm dứt hợp đồng rõ ràng bảo vệ cả hai bên.</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>What I've learned is that clear termination terms protect both parties.</t>
         </is>
@@ -7989,7 +7989,7 @@
           <t>Chúng tôi phải tuân thủ luật lao động Việt Nam.</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>We must comply with Vietnam's labor law.</t>
         </is>
@@ -8019,7 +8019,7 @@
           <t>Công ty tuân thủ mọi quy định về tuân thủ lao động.</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>The company follows all labor compliance regulations.</t>
         </is>
@@ -8049,7 +8049,7 @@
           <t>Việc không tuân thủ có thể dẫn đến bị phạt.</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
+      <c r="E254" s="2" t="inlineStr">
         <is>
           <t>Non-compliance can result in penalties.</t>
         </is>
@@ -8079,7 +8079,7 @@
           <t>Chúng tôi thực hiện kiểm tra tuân thủ lao động định kỳ.</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>We conduct regular labor compliance audits.</t>
         </is>
@@ -8109,7 +8109,7 @@
           <t>Mọi chính sách phải tuân thủ quy định hiện hành.</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>All policies must comply with current regulations.</t>
         </is>
@@ -8139,7 +8139,7 @@
           <t>Chúng tôi thực hiện kiểm tra nội bộ để đảm bảo tuân thủ luật lao động.</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
+      <c r="E257" s="2" t="inlineStr">
         <is>
           <t>We conduct an internal audit to ensure labor compliance.</t>
         </is>
@@ -8169,7 +8169,7 @@
           <t>Chính sách công ty phải phù hợp với quy định lao động hiện hành.</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
+      <c r="E258" s="2" t="inlineStr">
         <is>
           <t>The company policy must align with current labor regulations.</t>
         </is>
@@ -8199,7 +8199,7 @@
           <t>Việc không tuân thủ có thể dẫn đến bị xử phạt từ cơ quan lao động.</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr">
+      <c r="E259" s="2" t="inlineStr">
         <is>
           <t>Non-compliance can result in penalties from labor authorities.</t>
         </is>
@@ -8229,7 +8229,7 @@
           <t>Chúng tôi tư vấn cho khách hàng về các cập nhật luật lao động mỗi quý.</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
+      <c r="E260" s="2" t="inlineStr">
         <is>
           <t>We advise clients on labor law updates every quarter.</t>
         </is>
@@ -8259,7 +8259,7 @@
           <t>Mọi nội quy lao động phải được đăng ký với cơ quan chức năng.</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
+      <c r="E261" s="2" t="inlineStr">
         <is>
           <t>All internal labor regulations must be registered with the authority.</t>
         </is>
@@ -8289,7 +8289,7 @@
           <t>Tôi có thể giải thích những rủi ro tuân thủ chính đối với công ty của anh/chị.</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
+      <c r="E262" s="2" t="inlineStr">
         <is>
           <t>I can explain the key compliance risks for your company.</t>
         </is>
@@ -8319,7 +8319,7 @@
           <t>Chúng tôi khuyên nên cập nhật chính sách nội bộ mỗi khi luật lao động thay đổi.</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
+      <c r="E263" s="2" t="inlineStr">
         <is>
           <t>We advise updating internal policies whenever the labor law changes.</t>
         </is>
@@ -8349,7 +8349,7 @@
           <t>Dựa trên đánh giá của chúng tôi, công ty của anh/chị hầu như đã tuân thủ đầy đủ.</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
+      <c r="E264" s="2" t="inlineStr">
         <is>
           <t>Based on our assessment, your company is mostly compliant.</t>
         </is>
@@ -8379,7 +8379,7 @@
           <t>Tôi đề xuất thực hiện rà soát tuân thủ hai lần một năm.</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr">
+      <c r="E265" s="2" t="inlineStr">
         <is>
           <t>I recommend conducting a compliance review twice a year.</t>
         </is>
@@ -8409,7 +8409,7 @@
           <t>Để tôi làm rõ các hình phạt có thể xảy ra nếu không tuân thủ.</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr">
+      <c r="E266" s="2" t="inlineStr">
         <is>
           <t>Let me clarify the potential penalties for non-compliance.</t>
         </is>
@@ -8439,7 +8439,7 @@
           <t>Hãy chuyển sang báo cáo tình trạng tuân thủ lao động.</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr">
+      <c r="E267" s="2" t="inlineStr">
         <is>
           <t>Let's move on to the labor compliance status report.</t>
         </is>
@@ -8469,7 +8469,7 @@
           <t>Anh/chị có thể giải thích những thay đổi gần đây trong quy định lao động không?</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr">
+      <c r="E268" s="2" t="inlineStr">
         <is>
           <t>Could you explain the recent changes in labor regulations?</t>
         </is>
@@ -8499,7 +8499,7 @@
           <t>Tôi muốn nêu mối lo ngại về một khoảng trống tuân thủ có thể xảy ra.</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
+      <c r="E269" s="2" t="inlineStr">
         <is>
           <t>I'd like to raise a concern about a potential compliance gap.</t>
         </is>
@@ -8529,7 +8529,7 @@
           <t>Tóm lại, chúng ta sẽ cập nhật nội quy lao động trong tháng này.</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
+      <c r="E270" s="2" t="inlineStr">
         <is>
           <t>To summarize, we will update the internal labor regulations this month.</t>
         </is>
@@ -8559,7 +8559,7 @@
           <t>Hãy thống nhất kế hoạch hành động để khắc phục khoảng trống tuân thủ này.</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
+      <c r="E271" s="2" t="inlineStr">
         <is>
           <t>Let's agree on an action plan to close this compliance gap.</t>
         </is>
@@ -8589,7 +8589,7 @@
           <t>Thật ra, tôi nghĩ tuân thủ lao động là một nỗ lực liên tục, không phải việc làm một lần.</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr">
+      <c r="E272" s="2" t="inlineStr">
         <is>
           <t>Honestly, I think labor compliance is an ongoing effort, not a one time task.</t>
         </is>
@@ -8619,7 +8619,7 @@
           <t>Nếu phát hiện khoảng trống tuân thủ, tôi sẽ báo cáo và đề xuất cách khắc phục ngay.</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr">
+      <c r="E273" s="2" t="inlineStr">
         <is>
           <t>If I found a compliance gap, I'd report it and propose a fix immediately.</t>
         </is>
@@ -8649,7 +8649,7 @@
           <t>Theo kinh nghiệm của tôi, những vấn đề tuân thủ nhỏ có thể trở thành vấn đề lớn nếu bị bỏ qua.</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr">
+      <c r="E274" s="2" t="inlineStr">
         <is>
           <t>From my experience, small compliance issues can become big problems if ignored.</t>
         </is>
@@ -8679,7 +8679,7 @@
           <t>Tôi tin rằng cập nhật luật lao động là một phần công việc của chúng tôi.</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr">
+      <c r="E275" s="2" t="inlineStr">
         <is>
           <t>I believe staying updated on labor law is part of our job.</t>
         </is>
@@ -8709,9 +8709,9 @@
           <t>Điều tôi coi trọng nhất là giúp khách hàng tránh rủi ro tuân thủ trước khi nó xảy ra.</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>What I value most is helping clients avoid compliance risks before they happen.</t>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>What I value most is helping clients avoid compliance risks, before they happen.</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -8739,7 +8739,7 @@
           <t>Hạn chót trả lương là ngày 5 hàng tháng.</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr">
+      <c r="E277" s="2" t="inlineStr">
         <is>
           <t>The deadline for salary payment is the 5th of each month.</t>
         </is>
@@ -8769,9 +8769,9 @@
           <t>Vui lòng nộp bảng chấm công trước hạn chót.</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>Please submit your timesheet before the deadline.</t>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>Please submit your timesheet, before the deadline.</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -8799,7 +8799,7 @@
           <t>Chúng tôi đã trễ hạn khai thuế TNCN.</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr">
+      <c r="E279" s="2" t="inlineStr">
         <is>
           <t>We missed the deadline for PIT declaration.</t>
         </is>
@@ -8829,7 +8829,7 @@
           <t>Hạn chót đã được gia hạn thêm một tuần.</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr">
+      <c r="E280" s="2" t="inlineStr">
         <is>
           <t>The deadline has been extended by one week.</t>
         </is>
@@ -8859,9 +8859,9 @@
           <t>Chúng tôi có thể có thêm thời gian trước hạn chót không?</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>Can we have more time before the deadline?</t>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>Can we have more time, before the deadline?</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -8889,7 +8889,7 @@
           <t>Hạn nộp bảo hiểm xã hội là ngày cuối cùng của tháng.</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr">
+      <c r="E282" s="2" t="inlineStr">
         <is>
           <t>The deadline for social insurance submission is the last day of the month.</t>
         </is>
@@ -8919,7 +8919,7 @@
           <t>Chúng tôi luôn đặt hạn nội bộ sớm hơn hạn theo quy định pháp luật.</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
+      <c r="E283" s="2" t="inlineStr">
         <is>
           <t>We always set internal deadlines earlier than the legal ones.</t>
         </is>
@@ -8949,7 +8949,7 @@
           <t>Trễ hạn nộp thuế có thể dẫn đến phạt chậm nộp.</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr">
+      <c r="E284" s="2" t="inlineStr">
         <is>
           <t>Missing a tax deadline may result in a late payment penalty.</t>
         </is>
@@ -8979,7 +8979,7 @@
           <t>Vui lòng xác nhận hạn nộp với khách hàng trước khi gửi.</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr">
+      <c r="E285" s="2" t="inlineStr">
         <is>
           <t>Please confirm the deadline with the client before submission.</t>
         </is>
@@ -9009,7 +9009,7 @@
           <t>Chúng tôi theo dõi tất cả các hạn tuân thủ bằng lịch dùng chung.</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr">
+      <c r="E286" s="2" t="inlineStr">
         <is>
           <t>We track all compliance deadlines using a shared calendar.</t>
         </is>
@@ -9039,7 +9039,7 @@
           <t>Tôi có thể giải thích tất cả các hạn nộp theo quy định mà công ty phải tuân theo.</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr">
+      <c r="E287" s="2" t="inlineStr">
         <is>
           <t>I can explain all the statutory deadlines your company must follow.</t>
         </is>
@@ -9069,9 +9069,9 @@
           <t>Chúng tôi khuyên nên đặt nhắc nhở nội bộ trước mỗi hạn nộp.</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>We advise setting internal reminders before each deadline.</t>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>We advise setting internal reminders, before each deadline.</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -9099,7 +9099,7 @@
           <t>Dựa trên kinh nghiệm trước đây, nộp trễ thường gây ra các khoản phạt không cần thiết.</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr">
+      <c r="E289" s="2" t="inlineStr">
         <is>
           <t>Based on past experience, late submissions often cause unnecessary penalties.</t>
         </is>
@@ -9129,7 +9129,7 @@
           <t>Tôi đề xuất phân công một người theo dõi tất cả các hạn tuân thủ.</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr">
+      <c r="E290" s="2" t="inlineStr">
         <is>
           <t>I recommend assigning one person to monitor all compliance deadlines.</t>
         </is>
@@ -9159,7 +9159,7 @@
           <t>Để tôi làm rõ hạn nộp nào áp dụng cho trường hợp cụ thể của anh/chị.</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr">
+      <c r="E291" s="2" t="inlineStr">
         <is>
           <t>Let me clarify which deadline applies to your specific case.</t>
         </is>
@@ -9189,7 +9189,7 @@
           <t>Hãy chuyển sang rà soát các hạn tuân thủ trong tháng này.</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr">
+      <c r="E292" s="2" t="inlineStr">
         <is>
           <t>Let's move on to review this month's compliance deadlines.</t>
         </is>
@@ -9219,7 +9219,7 @@
           <t>Anh/chị có thể chia sẻ lịch các hạn nộp của tất cả khách hàng không?</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr">
+      <c r="E293" s="2" t="inlineStr">
         <is>
           <t>Could you share the deadline calendar for all our clients?</t>
         </is>
@@ -9249,7 +9249,7 @@
           <t>Tôi muốn nêu mối lo ngại về một hạn nộp chúng ta có thể bị trễ.</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr">
+      <c r="E294" s="2" t="inlineStr">
         <is>
           <t>I'd like to raise a concern about a deadline we might miss.</t>
         </is>
@@ -9279,7 +9279,7 @@
           <t>Tóm lại, tất cả các hạn nộp trong tuần này đã được xác nhận.</t>
         </is>
       </c>
-      <c r="E295" t="inlineStr">
+      <c r="E295" s="2" t="inlineStr">
         <is>
           <t>To summarize, all deadlines this week have been confirmed.</t>
         </is>
@@ -9309,7 +9309,7 @@
           <t>Hãy phân công người kiểm tra lại các hạn nộp trước khi gửi.</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr">
+      <c r="E296" s="2" t="inlineStr">
         <is>
           <t>Let's assign someone to double check the deadlines before submission.</t>
         </is>
@@ -9339,7 +9339,7 @@
           <t>Thật ra, tôi nghĩ việc đáp ứng đúng hạn giúp xây dựng niềm tin với khách hàng.</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr">
+      <c r="E297" s="2" t="inlineStr">
         <is>
           <t>Honestly, I think meeting deadlines builds trust with our clients.</t>
         </is>
@@ -9369,7 +9369,7 @@
           <t>Nếu một hạn nộp có nguy cơ bị trễ, tôi sẽ báo cho cả nhóm sớm.</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr">
+      <c r="E298" s="2" t="inlineStr">
         <is>
           <t>If a deadline was at risk, I'd flag it to the team early.</t>
         </is>
@@ -9399,7 +9399,7 @@
           <t>Theo kinh nghiệm của tôi, đặt hạn nội bộ sớm hơn luôn hữu ích.</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr">
+      <c r="E299" s="2" t="inlineStr">
         <is>
           <t>From my experience, setting internal deadlines earlier always helps.</t>
         </is>
@@ -9429,7 +9429,7 @@
           <t>Tôi tin rằng lịch dùng chung giúp tránh hầu hết các trường hợp trễ hạn.</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr">
+      <c r="E300" s="2" t="inlineStr">
         <is>
           <t>I believe a shared calendar prevents most missed deadlines.</t>
         </is>
@@ -9459,7 +9459,7 @@
           <t>Điều khiến tôi căng thẳng nhất là hạn nộp phụ thuộc vào phản hồi của khách hàng.</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr">
+      <c r="E301" s="2" t="inlineStr">
         <is>
           <t>What stresses me most is a deadline that depends on the client's response.</t>
         </is>
@@ -9489,7 +9489,7 @@
           <t>Có sai sót trong bảng lương tháng này.</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr">
+      <c r="E302" s="2" t="inlineStr">
         <is>
           <t>There was an error in this month's payroll.</t>
         </is>
@@ -9519,7 +9519,7 @@
           <t>Chúng tôi cần sửa lỗi ngay lập tức.</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr">
+      <c r="E303" s="2" t="inlineStr">
         <is>
           <t>We need to correct the mistake immediately.</t>
         </is>
@@ -9549,7 +9549,7 @@
           <t>Vui lòng kiểm tra kỹ trước khi nộp báo cáo.</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr">
+      <c r="E304" s="2" t="inlineStr">
         <is>
           <t>Please double-check before submitting the report.</t>
         </is>
@@ -9579,7 +9579,7 @@
           <t>Tôi xin lỗi vì sai sót trong phiếu lương của bạn.</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr">
+      <c r="E305" s="2" t="inlineStr">
         <is>
           <t>I apologize for the error in your payslip.</t>
         </is>
@@ -9609,7 +9609,7 @@
           <t>Phần điều chỉnh sẽ được phản ánh trong bảng lương tháng sau.</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr">
+      <c r="E306" s="2" t="inlineStr">
         <is>
           <t>The correction will be reflected in next month's payroll.</t>
         </is>
@@ -9639,7 +9639,7 @@
           <t>Nếu phát hiện sai sót trong bảng lương, chúng tôi phải sửa ngay lập tức.</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr">
+      <c r="E307" s="2" t="inlineStr">
         <is>
           <t>If we find an error in the payroll, we must correct it immediately.</t>
         </is>
@@ -9669,7 +9669,7 @@
           <t>Báo cáo điều chỉnh phải được nộp để giải thích sự thay đổi.</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr">
+      <c r="E308" s="2" t="inlineStr">
         <is>
           <t>A correction report must be submitted to explain the adjustment.</t>
         </is>
@@ -9699,7 +9699,7 @@
           <t>Chúng tôi xin lỗi vì sai sót và sẽ phát hành phiếu lương đã sửa.</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr">
+      <c r="E309" s="2" t="inlineStr">
         <is>
           <t>We apologize for the mistake and will issue a revised payslip.</t>
         </is>
@@ -9729,9 +9729,9 @@
           <t>Vui lòng thông báo cho chúng tôi trong vòng ba ngày nếu phát hiện sai lệch.</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>Please notify us within three days if you find any discrepancy.</t>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>Please notify us within three days, if you find any discrepancy.</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -9759,7 +9759,7 @@
           <t>Chúng tôi lưu lại nhật ký của tất cả các điều chỉnh để phục vụ kiểm toán.</t>
         </is>
       </c>
-      <c r="E311" t="inlineStr">
+      <c r="E311" s="2" t="inlineStr">
         <is>
           <t>We keep a log of all corrections for audit purposes.</t>
         </is>
@@ -9789,9 +9789,9 @@
           <t>Tôi có thể giải thích cách chúng tôi xử lý sai sót lương khi xảy ra.</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>I can explain how we handle payroll errors when they occur.</t>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>I can explain how we handle payroll errors, when they occur.</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -9819,7 +9819,7 @@
           <t>Chúng tôi khuyên nên báo cáo bất kỳ sai sót nào ngay khi phát hiện.</t>
         </is>
       </c>
-      <c r="E313" t="inlineStr">
+      <c r="E313" s="2" t="inlineStr">
         <is>
           <t>We advise reporting any error as soon as it is discovered.</t>
         </is>
@@ -9849,7 +9849,7 @@
           <t>Dựa trên rà soát của chúng tôi, sai sót này do lỗi nhập liệu.</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr">
+      <c r="E314" s="2" t="inlineStr">
         <is>
           <t>Based on our review, this error was caused by a data entry mistake.</t>
         </is>
@@ -9879,7 +9879,7 @@
           <t>Tôi đề xuất thêm bước kiểm tra chéo để tránh sai sót trong tương lai.</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr">
+      <c r="E315" s="2" t="inlineStr">
         <is>
           <t>I recommend adding a double check step to prevent future errors.</t>
         </is>
@@ -9909,7 +9909,7 @@
           <t>Để tôi làm rõ việc điều chỉnh sẽ ảnh hưởng thế nào đến phiếu lương tháng này.</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr">
+      <c r="E316" s="2" t="inlineStr">
         <is>
           <t>Let me clarify how the correction will affect this month's payslip.</t>
         </is>
@@ -9939,7 +9939,7 @@
           <t>Hãy chuyển sang thảo luận về sai sót lương của tháng trước.</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr">
+      <c r="E317" s="2" t="inlineStr">
         <is>
           <t>Let's move on to discuss the payroll error from last month.</t>
         </is>
@@ -9969,7 +9969,7 @@
           <t>Anh/chị có thể giải thích nguyên nhân gây ra sai sót này trong báo cáo không?</t>
         </is>
       </c>
-      <c r="E318" t="inlineStr">
+      <c r="E318" s="2" t="inlineStr">
         <is>
           <t>Could you explain what caused this error in the report?</t>
         </is>
@@ -9999,7 +9999,7 @@
           <t>Tôi muốn nêu mối lo ngại về việc điều chỉnh đang mất quá nhiều thời gian.</t>
         </is>
       </c>
-      <c r="E319" t="inlineStr">
+      <c r="E319" s="2" t="inlineStr">
         <is>
           <t>I'd like to raise a concern about how long the correction is taking.</t>
         </is>
@@ -10029,7 +10029,7 @@
           <t>Tóm lại, việc điều chỉnh sẽ hoàn tất vào ngày mai.</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr">
+      <c r="E320" s="2" t="inlineStr">
         <is>
           <t>To summarize, the correction will be completed by tomorrow.</t>
         </is>
@@ -10059,7 +10059,7 @@
           <t>Hãy thống nhất một quy trình để tránh loại sai sót này trong tương lai.</t>
         </is>
       </c>
-      <c r="E321" t="inlineStr">
+      <c r="E321" s="2" t="inlineStr">
         <is>
           <t>Let's agree on a process to prevent this type of error in the future.</t>
         </is>
@@ -10089,7 +10089,7 @@
           <t>Thật ra, tôi nghĩ cách chúng ta xử lý sai sót quan trọng hơn chính sai sót đó.</t>
         </is>
       </c>
-      <c r="E322" t="inlineStr">
+      <c r="E322" s="2" t="inlineStr">
         <is>
           <t>Honestly, I think how we handle an error matters more than the error itself.</t>
         </is>
@@ -10119,9 +10119,9 @@
           <t>Nếu tôi mắc sai sót, tôi sẽ thông báo cho khách hàng trước khi họ phát hiện ra.</t>
         </is>
       </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>If I made a mistake, I'd inform the client before they noticed it.</t>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>If I made a mistake, I'd inform the client, before they noticed it.</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -10149,7 +10149,7 @@
           <t>Theo kinh nghiệm của tôi, hầu hết sai sót đến từ việc nhập liệu vội vàng.</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr">
+      <c r="E324" s="2" t="inlineStr">
         <is>
           <t>From my experience, most errors come from rushed data entry.</t>
         </is>
@@ -10179,7 +10179,7 @@
           <t>Tôi tin rằng bước kiểm tra chéo giúp ngăn ngừa hầu hết sai sót về lương.</t>
         </is>
       </c>
-      <c r="E325" t="inlineStr">
+      <c r="E325" s="2" t="inlineStr">
         <is>
           <t>I believe a double check step prevents most payroll errors.</t>
         </is>
@@ -10209,7 +10209,7 @@
           <t>Điều tôi rút ra được là nhận lỗi nhanh chóng giúp nhận được nhiều sự tôn trọng hơn.</t>
         </is>
       </c>
-      <c r="E326" t="inlineStr">
+      <c r="E326" s="2" t="inlineStr">
         <is>
           <t>What I've learned is that owning up to an error quickly earns more respect.</t>
         </is>
@@ -10239,7 +10239,7 @@
           <t>Chúng ta có thể sắp xếp một cuộc họp vào sáng mai được không?</t>
         </is>
       </c>
-      <c r="E327" t="inlineStr">
+      <c r="E327" s="2" t="inlineStr">
         <is>
           <t>Can we schedule a meeting for tomorrow morning?</t>
         </is>
@@ -10269,7 +10269,7 @@
           <t>Tôi sẽ gửi lời mời họp qua email.</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr">
+      <c r="E328" s="2" t="inlineStr">
         <is>
           <t>I will send the meeting invitation by email.</t>
         </is>
@@ -10299,7 +10299,7 @@
           <t>Xin lỗi, tôi sẽ đến trễ cuộc họp năm phút.</t>
         </is>
       </c>
-      <c r="E329" t="inlineStr">
+      <c r="E329" s="2" t="inlineStr">
         <is>
           <t>Sorry, I will be five minutes late for the meeting.</t>
         </is>
@@ -10329,7 +10329,7 @@
           <t>Anh/chị có thể nhắc lại được không?</t>
         </is>
       </c>
-      <c r="E330" t="inlineStr">
+      <c r="E330" s="2" t="inlineStr">
         <is>
           <t>Could you please repeat that?</t>
         </is>
@@ -10359,7 +10359,7 @@
           <t>Cảm ơn mọi người đã tham gia cuộc họp hôm nay.</t>
         </is>
       </c>
-      <c r="E331" t="inlineStr">
+      <c r="E331" s="2" t="inlineStr">
         <is>
           <t>Thank you all for joining today's meeting.</t>
         </is>
@@ -10389,9 +10389,9 @@
           <t>Vui lòng chuẩn bị chương trình họp trước khi bắt đầu.</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>Please prepare the meeting agenda before we start.</t>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>Please prepare the meeting agenda, before we start.</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -10419,7 +10419,7 @@
           <t>Tôi sẽ ghi chú và chia sẻ biên bản họp sau đó.</t>
         </is>
       </c>
-      <c r="E333" t="inlineStr">
+      <c r="E333" s="2" t="inlineStr">
         <is>
           <t>I will take notes and share the minutes afterward.</t>
         </is>
@@ -10449,7 +10449,7 @@
           <t>Chúng ta cần xác nhận đặt phòng họp trước.</t>
         </is>
       </c>
-      <c r="E334" t="inlineStr">
+      <c r="E334" s="2" t="inlineStr">
         <is>
           <t>We need to confirm the meeting room booking in advance.</t>
         </is>
@@ -10479,7 +10479,7 @@
           <t>Hãy giữ cuộc họp này trong ba mươi phút.</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr">
+      <c r="E335" s="2" t="inlineStr">
         <is>
           <t>Let's keep this meeting to thirty minutes.</t>
         </is>
@@ -10509,7 +10509,7 @@
           <t>Tôi sẽ mời thêm bộ phận kế toán tham gia buổi thảo luận này.</t>
         </is>
       </c>
-      <c r="E336" t="inlineStr">
+      <c r="E336" s="2" t="inlineStr">
         <is>
           <t>I will loop in the accounting team for this discussion.</t>
         </is>
@@ -10539,9 +10539,9 @@
           <t>Tôi đề xuất gửi chương trình họp trước một ngày.</t>
         </is>
       </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>I recommend sending the agenda a day before the meeting.</t>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>I recommend sending the agenda a day, before the meeting.</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -10569,7 +10569,7 @@
           <t>Để tôi giải thích mục đích của cuộc họp hôm nay.</t>
         </is>
       </c>
-      <c r="E338" t="inlineStr">
+      <c r="E338" s="2" t="inlineStr">
         <is>
           <t>Let me explain the purpose of today's meeting.</t>
         </is>
@@ -10599,7 +10599,7 @@
           <t>Tôi đề xuất giới hạn mỗi chủ đề trong mười phút.</t>
         </is>
       </c>
-      <c r="E339" t="inlineStr">
+      <c r="E339" s="2" t="inlineStr">
         <is>
           <t>I suggest we limit each topic to ten minutes.</t>
         </is>
@@ -10629,7 +10629,7 @@
           <t>Dựa trên thảo luận hôm nay, tôi đề xuất một cuộc họp tiếp theo vào tuần sau.</t>
         </is>
       </c>
-      <c r="E340" t="inlineStr">
+      <c r="E340" s="2" t="inlineStr">
         <is>
           <t>Based on today's discussion, I recommend a follow-up meeting next week.</t>
         </is>
@@ -10659,7 +10659,7 @@
           <t>Tôi khuyên nên mời khách hàng tham gia cuộc họp tiếp theo.</t>
         </is>
       </c>
-      <c r="E341" t="inlineStr">
+      <c r="E341" s="2" t="inlineStr">
         <is>
           <t>I would advise inviting the client to the next meeting.</t>
         </is>
@@ -10689,7 +10689,7 @@
           <t>Hãy bắt đầu thôi, mọi người đã có mặt đầy đủ.</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr">
+      <c r="E342" s="2" t="inlineStr">
         <is>
           <t>Let's get started, everyone is here.</t>
         </is>
@@ -10719,9 +10719,9 @@
           <t>Mọi người vui lòng tắt micro khi không phát biểu được không?</t>
         </is>
       </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>Could everyone please mute their microphone when not speaking?</t>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>Could everyone please mute their microphone, when not speaking?</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -10749,7 +10749,7 @@
           <t>Hãy lần lượt chia sẻ cập nhật của mỗi người.</t>
         </is>
       </c>
-      <c r="E344" t="inlineStr">
+      <c r="E344" s="2" t="inlineStr">
         <is>
           <t>Let's go around the room and share updates.</t>
         </is>
@@ -10779,7 +10779,7 @@
           <t>Tôi nghĩ chúng ta đã trao đổi hết mọi thứ rồi, hãy kết thúc buổi họp.</t>
         </is>
       </c>
-      <c r="E345" t="inlineStr">
+      <c r="E345" s="2" t="inlineStr">
         <is>
           <t>I think we've covered everything, let's wrap up.</t>
         </is>
@@ -10809,9 +10809,9 @@
           <t>Hãy đặt lịch cho cuộc họp tiếp theo trước khi kết thúc.</t>
         </is>
       </c>
-      <c r="E346" t="inlineStr">
-        <is>
-          <t>Let's schedule the next meeting before we go.</t>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>Let's schedule the next meeting, before we go.</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -10839,7 +10839,7 @@
           <t>Thật ra, tôi nghĩ các cuộc họp ngắn thường hiệu quả hơn.</t>
         </is>
       </c>
-      <c r="E347" t="inlineStr">
+      <c r="E347" s="2" t="inlineStr">
         <is>
           <t>Honestly, I think shorter meetings are usually more productive.</t>
         </is>
@@ -10869,7 +10869,7 @@
           <t>Nếu cuộc họp kéo dài quá lâu, tôi sẽ khéo léo đề nghị kết thúc.</t>
         </is>
       </c>
-      <c r="E348" t="inlineStr">
+      <c r="E348" s="2" t="inlineStr">
         <is>
           <t>If a meeting runs too long, I'd politely suggest wrapping up.</t>
         </is>
@@ -10899,7 +10899,7 @@
           <t>Theo kinh nghiệm của tôi, chương trình họp rõ ràng giúp tiết kiệm thời gian cho mọi người.</t>
         </is>
       </c>
-      <c r="E349" t="inlineStr">
+      <c r="E349" s="2" t="inlineStr">
         <is>
           <t>From my experience, a clear agenda saves everyone's time.</t>
         </is>
@@ -10929,7 +10929,7 @@
           <t>Tôi tin rằng mỗi cuộc họp nên kết thúc với các công việc cụ thể cần làm.</t>
         </is>
       </c>
-      <c r="E350" t="inlineStr">
+      <c r="E350" s="2" t="inlineStr">
         <is>
           <t>I believe every meeting should end with clear action items.</t>
         </is>
@@ -10959,7 +10959,7 @@
           <t>Điều tôi không thích nhất là một cuộc họp không có mục đích rõ ràng.</t>
         </is>
       </c>
-      <c r="E351" t="inlineStr">
+      <c r="E351" s="2" t="inlineStr">
         <is>
           <t>What I dislike most is a meeting without a clear purpose.</t>
         </is>
@@ -10989,7 +10989,7 @@
           <t>Tôi nghĩ chúng ta gặp vấn đề với dữ liệu tháng này.</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr">
+      <c r="E352" s="2" t="inlineStr">
         <is>
           <t>I think we have a problem with this month's data.</t>
         </is>
@@ -11019,7 +11019,7 @@
           <t>Tôi có thể giải thích vấn đề này cho anh/chị được không?</t>
         </is>
       </c>
-      <c r="E353" t="inlineStr">
+      <c r="E353" s="2" t="inlineStr">
         <is>
           <t>Can I explain the issue to you?</t>
         </is>
@@ -11049,7 +11049,7 @@
           <t>Việc này khẩn cấp, chúng ta cần sửa ngay hôm nay.</t>
         </is>
       </c>
-      <c r="E354" t="inlineStr">
+      <c r="E354" s="2" t="inlineStr">
         <is>
           <t>This is urgent, we need to fix it today.</t>
         </is>
@@ -11079,7 +11079,7 @@
           <t>Tôi không chắc điều gì đã gây ra vấn đề này.</t>
         </is>
       </c>
-      <c r="E355" t="inlineStr">
+      <c r="E355" s="2" t="inlineStr">
         <is>
           <t>I'm not sure what caused this problem.</t>
         </is>
@@ -11109,7 +11109,7 @@
           <t>Hãy nói về vấn đề này sau bữa trưa nhé.</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr">
+      <c r="E356" s="2" t="inlineStr">
         <is>
           <t>Let's talk about this issue after lunch.</t>
         </is>
@@ -11139,7 +11139,7 @@
           <t>Chúng tôi phát hiện sự chênh lệch trong dữ liệu của khách hàng sáng nay.</t>
         </is>
       </c>
-      <c r="E357" t="inlineStr">
+      <c r="E357" s="2" t="inlineStr">
         <is>
           <t>We identified a discrepancy in the client's data this morning.</t>
         </is>
@@ -11169,7 +11169,7 @@
           <t>Hãy chia nhỏ vấn đề này ra để dễ xử lý.</t>
         </is>
       </c>
-      <c r="E358" t="inlineStr">
+      <c r="E358" s="2" t="inlineStr">
         <is>
           <t>Let's break down the issue into smaller parts.</t>
         </is>
@@ -11199,7 +11199,7 @@
           <t>Chúng ta cần báo cáo vấn đề này lên quản lý phụ trách khách hàng.</t>
         </is>
       </c>
-      <c r="E359" t="inlineStr">
+      <c r="E359" s="2" t="inlineStr">
         <is>
           <t>We need to escalate this issue to the account manager.</t>
         </is>
@@ -11229,7 +11229,7 @@
           <t>Nguyên nhân gốc rễ của vấn đề vẫn chưa rõ ràng.</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr">
+      <c r="E360" s="2" t="inlineStr">
         <is>
           <t>The root cause of the problem is still unclear.</t>
         </is>
@@ -11259,7 +11259,7 @@
           <t>Hãy ghi lại vấn đề này để tham khảo sau này.</t>
         </is>
       </c>
-      <c r="E361" t="inlineStr">
+      <c r="E361" s="2" t="inlineStr">
         <is>
           <t>Let's document this issue for future reference.</t>
         </is>
@@ -11289,7 +11289,7 @@
           <t>Để tôi giải thích chi tiết nguyên nhân gây ra vấn đề này.</t>
         </is>
       </c>
-      <c r="E362" t="inlineStr">
+      <c r="E362" s="2" t="inlineStr">
         <is>
           <t>Let me explain what caused this issue in detail.</t>
         </is>
@@ -11319,9 +11319,9 @@
           <t>Tôi đề xuất xử lý vấn đề này trước khi nó ảnh hưởng đến các phòng ban khác.</t>
         </is>
       </c>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>I recommend addressing this issue before it affects other departments.</t>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>I recommend addressing this issue, before it affects other departments.</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -11349,7 +11349,7 @@
           <t>Dựa trên phân tích của tôi, vấn đề này có thể là lỗi hệ thống.</t>
         </is>
       </c>
-      <c r="E364" t="inlineStr">
+      <c r="E364" s="2" t="inlineStr">
         <is>
           <t>Based on my analysis, this issue is likely a system error.</t>
         </is>
@@ -11379,9 +11379,9 @@
           <t>Tôi đề xuất áp dụng giải pháp tạm thời trong khi chúng ta điều tra thêm.</t>
         </is>
       </c>
-      <c r="E365" t="inlineStr">
-        <is>
-          <t>I suggest we set up a temporary solution while we investigate further.</t>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>I suggest we set up a temporary solution, while we investigate further.</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -11409,7 +11409,7 @@
           <t>Hãy để tôi trình bày cách chúng tôi dự định giải quyết vấn đề này.</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr">
+      <c r="E366" s="2" t="inlineStr">
         <is>
           <t>Let me walk you through how we plan to resolve this.</t>
         </is>
@@ -11439,7 +11439,7 @@
           <t>Hãy chuyển sang vấn đề chúng ta đã thảo luận trước đó.</t>
         </is>
       </c>
-      <c r="E367" t="inlineStr">
+      <c r="E367" s="2" t="inlineStr">
         <is>
           <t>Let's move on to the issue we discussed earlier.</t>
         </is>
@@ -11469,7 +11469,7 @@
           <t>Anh/chị có thể trình bày điều gì đã xảy ra không?</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr">
+      <c r="E368" s="2" t="inlineStr">
         <is>
           <t>Could you walk us through what went wrong?</t>
         </is>
@@ -11499,7 +11499,7 @@
           <t>Tôi muốn nêu mối lo ngại về vấn đề lặp lại này.</t>
         </is>
       </c>
-      <c r="E369" t="inlineStr">
+      <c r="E369" s="2" t="inlineStr">
         <is>
           <t>I'd like to raise a concern about this recurring problem.</t>
         </is>
@@ -11529,7 +11529,7 @@
           <t>Tóm lại, chúng ta đã thống nhất kế hoạch khắc phục trước thứ Sáu.</t>
         </is>
       </c>
-      <c r="E370" t="inlineStr">
+      <c r="E370" s="2" t="inlineStr">
         <is>
           <t>To summarize, we agreed on a plan to fix this by Friday.</t>
         </is>
@@ -11559,7 +11559,7 @@
           <t>Hãy phân công người theo dõi sát vấn đề này.</t>
         </is>
       </c>
-      <c r="E371" t="inlineStr">
+      <c r="E371" s="2" t="inlineStr">
         <is>
           <t>Let's assign someone to monitor this issue closely.</t>
         </is>
@@ -11589,7 +11589,7 @@
           <t>Thật ra, tôi nghĩ chúng ta nên xử lý vấn đề ngay khi nó xuất hiện.</t>
         </is>
       </c>
-      <c r="E372" t="inlineStr">
+      <c r="E372" s="2" t="inlineStr">
         <is>
           <t>Honestly, I think we should address problems as soon as they appear.</t>
         </is>
@@ -11619,7 +11619,7 @@
           <t>Nếu thấy một vấn đề lặp lại, tôi sẽ tìm hiểu sâu hơn về nguyên nhân gốc rễ.</t>
         </is>
       </c>
-      <c r="E373" t="inlineStr">
+      <c r="E373" s="2" t="inlineStr">
         <is>
           <t>If I noticed a recurring issue, I'd dig deeper into the root cause.</t>
         </is>
@@ -11649,7 +11649,7 @@
           <t>Theo kinh nghiệm của tôi, hầu hết vấn đề đến từ việc thiếu giao tiếp.</t>
         </is>
       </c>
-      <c r="E374" t="inlineStr">
+      <c r="E374" s="2" t="inlineStr">
         <is>
           <t>From my experience, most problems come from a lack of communication.</t>
         </is>
@@ -11679,7 +11679,7 @@
           <t>Tôi tin rằng thẳng thắn về vấn đề giúp xây dựng niềm tin hơn là che giấu nó.</t>
         </is>
       </c>
-      <c r="E375" t="inlineStr">
+      <c r="E375" s="2" t="inlineStr">
         <is>
           <t>I believe being honest about a problem builds more trust than hiding it.</t>
         </is>
@@ -11709,7 +11709,7 @@
           <t>Điều quan trọng nhất với tôi là tìm ra giải pháp, không phải đổ lỗi.</t>
         </is>
       </c>
-      <c r="E376" t="inlineStr">
+      <c r="E376" s="2" t="inlineStr">
         <is>
           <t>What matters most to me is finding a solution, not placing blame.</t>
         </is>
@@ -11739,7 +11739,7 @@
           <t>Tôi hiểu anh/chị đang khó chịu, hãy cùng nói chuyện về việc này.</t>
         </is>
       </c>
-      <c r="E377" t="inlineStr">
+      <c r="E377" s="2" t="inlineStr">
         <is>
           <t>I understand you are upset, let's talk about it.</t>
         </is>
@@ -11769,7 +11769,7 @@
           <t>Tôi xin lỗi vì sự hiểu lầm này.</t>
         </is>
       </c>
-      <c r="E378" t="inlineStr">
+      <c r="E378" s="2" t="inlineStr">
         <is>
           <t>I'm sorry for the misunderstanding.</t>
         </is>
@@ -11799,7 +11799,7 @@
           <t>Chúng ta có thể cùng tìm ra giải pháp không?</t>
         </is>
       </c>
-      <c r="E379" t="inlineStr">
+      <c r="E379" s="2" t="inlineStr">
         <is>
           <t>Can we find a solution together?</t>
         </is>
@@ -11829,7 +11829,7 @@
           <t>Tôi không có ý làm anh/chị khó chịu.</t>
         </is>
       </c>
-      <c r="E380" t="inlineStr">
+      <c r="E380" s="2" t="inlineStr">
         <is>
           <t>I did not mean to upset you.</t>
         </is>
@@ -11859,7 +11859,7 @@
           <t>Hãy bình tĩnh và trao đổi rõ ràng về việc này.</t>
         </is>
       </c>
-      <c r="E381" t="inlineStr">
+      <c r="E381" s="2" t="inlineStr">
         <is>
           <t>Let's stay calm and discuss this clearly.</t>
         </is>
@@ -11889,7 +11889,7 @@
           <t>Tôi hiểu sự bức xúc của anh/chị và tôi muốn giúp giải quyết việc này.</t>
         </is>
       </c>
-      <c r="E382" t="inlineStr">
+      <c r="E382" s="2" t="inlineStr">
         <is>
           <t>I understand your frustration, and I want to help resolve this.</t>
         </is>
@@ -11919,7 +11919,7 @@
           <t>Hãy tập trung vào sự việc thay vì cảm xúc.</t>
         </is>
       </c>
-      <c r="E383" t="inlineStr">
+      <c r="E383" s="2" t="inlineStr">
         <is>
           <t>Let's focus on the facts rather than the emotions.</t>
         </is>
@@ -11949,7 +11949,7 @@
           <t>Tôi muốn nghe quan điểm của anh/chị về việc này.</t>
         </is>
       </c>
-      <c r="E384" t="inlineStr">
+      <c r="E384" s="2" t="inlineStr">
         <is>
           <t>I'd like to hear your perspective on this matter.</t>
         </is>
@@ -11979,7 +11979,7 @@
           <t>Chúng ta nên tìm một giải pháp dung hòa cho cả hai bên.</t>
         </is>
       </c>
-      <c r="E385" t="inlineStr">
+      <c r="E385" s="2" t="inlineStr">
         <is>
           <t>We should find a compromise that works for both sides.</t>
         </is>
@@ -12009,7 +12009,7 @@
           <t>Hãy thống nhất các bước tiếp theo để tránh việc này lặp lại.</t>
         </is>
       </c>
-      <c r="E386" t="inlineStr">
+      <c r="E386" s="2" t="inlineStr">
         <is>
           <t>Let's agree on the next steps to avoid this happening again.</t>
         </is>
@@ -12039,7 +12039,7 @@
           <t>Tôi hiểu tình huống này khá khó chịu, để tôi giải thích chuyện đã xảy ra.</t>
         </is>
       </c>
-      <c r="E387" t="inlineStr">
+      <c r="E387" s="2" t="inlineStr">
         <is>
           <t>I understand this situation is frustrating, let me explain what happened.</t>
         </is>
@@ -12069,7 +12069,7 @@
           <t>Tôi đề xuất chúng ta nên đối mặt trực tiếp thay vì né tránh vấn đề này.</t>
         </is>
       </c>
-      <c r="E388" t="inlineStr">
+      <c r="E388" s="2" t="inlineStr">
         <is>
           <t>I recommend we address this directly rather than avoid it.</t>
         </is>
@@ -12099,7 +12099,7 @@
           <t>Dựa trên ý kiến của cả hai bên, tôi đề xuất một giải pháp trung hòa.</t>
         </is>
       </c>
-      <c r="E389" t="inlineStr">
+      <c r="E389" s="2" t="inlineStr">
         <is>
           <t>Based on both sides' input, I suggest a middle-ground solution.</t>
         </is>
@@ -12129,7 +12129,7 @@
           <t>Tôi khuyên nên trao đổi việc này riêng tư.</t>
         </is>
       </c>
-      <c r="E390" t="inlineStr">
+      <c r="E390" s="2" t="inlineStr">
         <is>
           <t>I would advise having this conversation in private.</t>
         </is>
@@ -12159,7 +12159,7 @@
           <t>Để tôi làm rõ ý định của mình để tránh hiểu lầm thêm.</t>
         </is>
       </c>
-      <c r="E391" t="inlineStr">
+      <c r="E391" s="2" t="inlineStr">
         <is>
           <t>Let me clarify my intention so there is no more misunderstanding.</t>
         </is>
@@ -12189,7 +12189,7 @@
           <t>Tôi muốn nêu một vấn đề nhạy cảm cần được giải quyết.</t>
         </is>
       </c>
-      <c r="E392" t="inlineStr">
+      <c r="E392" s="2" t="inlineStr">
         <is>
           <t>I'd like to raise a sensitive issue we need to resolve.</t>
         </is>
@@ -12219,7 +12219,7 @@
           <t>Chúng ta có thể dành chút thời gian để nghe cả hai phía không?</t>
         </is>
       </c>
-      <c r="E393" t="inlineStr">
+      <c r="E393" s="2" t="inlineStr">
         <is>
           <t>Could we take a moment to hear both sides of this?</t>
         </is>
@@ -12249,9 +12249,9 @@
           <t>Hãy tìm điểm chung trước khi tiếp tục.</t>
         </is>
       </c>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>Let's find common ground before we continue.</t>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>Let's find common ground, before we continue.</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
@@ -12279,7 +12279,7 @@
           <t>Tóm lại, cả hai bên đã đồng ý cùng tiến về phía trước.</t>
         </is>
       </c>
-      <c r="E395" t="inlineStr">
+      <c r="E395" s="2" t="inlineStr">
         <is>
           <t>To summarize, both sides agreed to move forward together.</t>
         </is>
@@ -12309,9 +12309,9 @@
           <t>Hãy thống nhất sẽ xem lại việc này nếu vấn đề lặp lại.</t>
         </is>
       </c>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>Let's agree to revisit this if the issue comes up again.</t>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>Let's agree to revisit this, if the issue comes up again.</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
@@ -12339,7 +12339,7 @@
           <t>Thật ra, tôi nghĩ hầu hết xung đột đến từ kỳ vọng không rõ ràng.</t>
         </is>
       </c>
-      <c r="E397" t="inlineStr">
+      <c r="E397" s="2" t="inlineStr">
         <is>
           <t>Honestly, I think most conflicts come from unclear expectations.</t>
         </is>
@@ -12369,7 +12369,7 @@
           <t>Nếu đồng nghiệp không đồng ý với tôi, tôi sẽ lắng nghe trước khi phản hồi.</t>
         </is>
       </c>
-      <c r="E398" t="inlineStr">
+      <c r="E398" s="2" t="inlineStr">
         <is>
           <t>If a colleague disagreed with me, I'd listen before responding.</t>
         </is>
@@ -12399,7 +12399,7 @@
           <t>Theo kinh nghiệm của tôi, giữ bình tĩnh giúp hạ nhiệt hầu hết các bất đồng.</t>
         </is>
       </c>
-      <c r="E399" t="inlineStr">
+      <c r="E399" s="2" t="inlineStr">
         <is>
           <t>From my experience, staying calm de-escalates most disagreements.</t>
         </is>
@@ -12429,7 +12429,7 @@
           <t>Tôi tin rằng giải quyết xung đột sớm giúp tránh những vấn đề lớn hơn sau này.</t>
         </is>
       </c>
-      <c r="E400" t="inlineStr">
+      <c r="E400" s="2" t="inlineStr">
         <is>
           <t>I believe addressing conflict early prevents bigger problems later.</t>
         </is>
@@ -12459,7 +12459,7 @@
           <t>Điều tôi rút ra được là lắng nghe quan trọng hơn việc chứng minh mình đúng.</t>
         </is>
       </c>
-      <c r="E401" t="inlineStr">
+      <c r="E401" s="2" t="inlineStr">
         <is>
           <t>What I've learned is that listening matters more than being right.</t>
         </is>
@@ -12489,7 +12489,7 @@
           <t>Tôi sẽ gửi email cho anh/chị kèm thông tin chi tiết.</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr">
+      <c r="E402" s="2" t="inlineStr">
         <is>
           <t>I will send you an email with the details.</t>
         </is>
@@ -12519,7 +12519,7 @@
           <t>Vui lòng kiểm tra hộp thư để xem tin nhắn của tôi.</t>
         </is>
       </c>
-      <c r="E403" t="inlineStr">
+      <c r="E403" s="2" t="inlineStr">
         <is>
           <t>Please check your inbox for my message.</t>
         </is>
@@ -12549,7 +12549,7 @@
           <t>Tôi đã đính kèm tệp trong email này.</t>
         </is>
       </c>
-      <c r="E404" t="inlineStr">
+      <c r="E404" s="2" t="inlineStr">
         <is>
           <t>I have attached the file to this email.</t>
         </is>
@@ -12579,7 +12579,7 @@
           <t>Vui lòng phản hồi email này càng sớm càng tốt.</t>
         </is>
       </c>
-      <c r="E405" t="inlineStr">
+      <c r="E405" s="2" t="inlineStr">
         <is>
           <t>Please reply to this email as soon as possible.</t>
         </is>
@@ -12609,7 +12609,7 @@
           <t>Cảm ơn anh/chị đã phản hồi nhanh chóng.</t>
         </is>
       </c>
-      <c r="E406" t="inlineStr">
+      <c r="E406" s="2" t="inlineStr">
         <is>
           <t>Thank you for your quick response.</t>
         </is>
@@ -12639,7 +12639,7 @@
           <t>Tôi viết email này để theo dõi lại cuộc trao đổi trước đây của chúng ta.</t>
         </is>
       </c>
-      <c r="E407" t="inlineStr">
+      <c r="E407" s="2" t="inlineStr">
         <is>
           <t>I am writing to follow up on our previous discussion.</t>
         </is>
@@ -12669,7 +12669,7 @@
           <t>Vui lòng xem báo cáo đính kèm để kiểm tra.</t>
         </is>
       </c>
-      <c r="E408" t="inlineStr">
+      <c r="E408" s="2" t="inlineStr">
         <is>
           <t>Please find the attached report for your review.</t>
         </is>
@@ -12699,9 +12699,9 @@
           <t>Tôi rất mong anh/chị có thể xác nhận trước cuối ngày.</t>
         </is>
       </c>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>I would appreciate it if you could confirm by end of day.</t>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>I would appreciate it, if you could confirm by end of day.</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
@@ -12729,9 +12729,9 @@
           <t>Vui lòng cho tôi biết nếu anh/chị có câu hỏi nào về email này.</t>
         </is>
       </c>
-      <c r="E410" t="inlineStr">
-        <is>
-          <t>Let me know if you have any questions regarding this email.</t>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>Let me know, if you have any questions regarding this email.</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
@@ -12759,7 +12759,7 @@
           <t>Tôi đã CC bộ phận kế toán vào email này để mọi người nắm thông tin.</t>
         </is>
       </c>
-      <c r="E411" t="inlineStr">
+      <c r="E411" s="2" t="inlineStr">
         <is>
           <t>I am copying the accounting team on this email for visibility.</t>
         </is>
@@ -12789,7 +12789,7 @@
           <t>Tôi muốn giải thích tình huống này bằng văn bản để rõ ràng hơn.</t>
         </is>
       </c>
-      <c r="E412" t="inlineStr">
+      <c r="E412" s="2" t="inlineStr">
         <is>
           <t>I would like to explain the situation in writing for clarity.</t>
         </is>
@@ -12819,7 +12819,7 @@
           <t>Tôi đề xuất viết email ngắn gọn và đi thẳng vào vấn đề.</t>
         </is>
       </c>
-      <c r="E413" t="inlineStr">
+      <c r="E413" s="2" t="inlineStr">
         <is>
           <t>I recommend keeping the email concise and to the point.</t>
         </is>
@@ -12849,7 +12849,7 @@
           <t>Dựa trên tin nhắn của anh/chị, tôi hiểu rằng hạn nộp đã thay đổi.</t>
         </is>
       </c>
-      <c r="E414" t="inlineStr">
+      <c r="E414" s="2" t="inlineStr">
         <is>
           <t>Based on your message, I understand the deadline has changed.</t>
         </is>
@@ -12879,7 +12879,7 @@
           <t>Tôi đề xuất xác nhận thỏa thuận này bằng văn bản trước khi tiến hành.</t>
         </is>
       </c>
-      <c r="E415" t="inlineStr">
+      <c r="E415" s="2" t="inlineStr">
         <is>
           <t>I suggest we confirm this agreement in writing before proceeding.</t>
         </is>
@@ -12909,7 +12909,7 @@
           <t>Để tôi làm rõ email trước đó của mình để tránh nhầm lẫn.</t>
         </is>
       </c>
-      <c r="E416" t="inlineStr">
+      <c r="E416" s="2" t="inlineStr">
         <is>
           <t>Let me clarify my previous email to avoid confusion.</t>
         </is>
@@ -12939,9 +12939,9 @@
           <t>Tôi đã gửi email theo dõi sau cuộc họp hôm qua.</t>
         </is>
       </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>I sent a follow-up email after our meeting yesterday.</t>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>I sent a follow-up email, after our meeting yesterday.</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -12969,9 +12969,9 @@
           <t>Anh/chị có thể xác nhận quyết định này bằng văn bản sau cuộc họp không?</t>
         </is>
       </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>Could you confirm this decision in writing after the meeting?</t>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>Could you confirm this decision in writing, after the meeting?</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
@@ -12999,7 +12999,7 @@
           <t>Tôi muốn nêu một điểm đã được đề cập trong chuỗi email.</t>
         </is>
       </c>
-      <c r="E419" t="inlineStr">
+      <c r="E419" s="2" t="inlineStr">
         <is>
           <t>I'd like to raise a point that was mentioned in the email thread.</t>
         </is>
@@ -13029,7 +13029,7 @@
           <t>Tóm lại, tôi sẽ gửi biên bản họp qua email hôm nay.</t>
         </is>
       </c>
-      <c r="E420" t="inlineStr">
+      <c r="E420" s="2" t="inlineStr">
         <is>
           <t>To summarize, I will send meeting minutes by email today.</t>
         </is>
@@ -13059,9 +13059,9 @@
           <t>Hãy ghi lại các việc cần làm bằng văn bản trước khi kết thúc cuộc họp.</t>
         </is>
       </c>
-      <c r="E421" t="inlineStr">
-        <is>
-          <t>Let's put the action items in writing before we close the meeting.</t>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>Let's put the action items in writing, before we close the meeting.</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -13089,7 +13089,7 @@
           <t>Thật ra, tôi nghĩ tiêu đề email rõ ràng giúp tiết kiệm thời gian cho mọi người.</t>
         </is>
       </c>
-      <c r="E422" t="inlineStr">
+      <c r="E422" s="2" t="inlineStr">
         <is>
           <t>Honestly, I think a clear subject line saves everyone time.</t>
         </is>
@@ -13119,7 +13119,7 @@
           <t>Nếu một email không rõ ràng, tôi sẽ hỏi lại thay vì tự suy đoán.</t>
         </is>
       </c>
-      <c r="E423" t="inlineStr">
+      <c r="E423" s="2" t="inlineStr">
         <is>
           <t>If an email sounded unclear, I'd ask for clarification instead of assuming.</t>
         </is>
@@ -13149,7 +13149,7 @@
           <t>Theo kinh nghiệm của tôi, các thỏa thuận quan trọng nên luôn được xác nhận bằng văn bản.</t>
         </is>
       </c>
-      <c r="E424" t="inlineStr">
+      <c r="E424" s="2" t="inlineStr">
         <is>
           <t>From my experience, important agreements should always be confirmed in writing.</t>
         </is>
@@ -13179,7 +13179,7 @@
           <t>Tôi tin rằng giọng văn lịch sự trong email giúp tránh những hiểu lầm không cần thiết.</t>
         </is>
       </c>
-      <c r="E425" t="inlineStr">
+      <c r="E425" s="2" t="inlineStr">
         <is>
           <t>I believe a polite tone in emails prevents unnecessary misunderstandings.</t>
         </is>
@@ -13209,7 +13209,7 @@
           <t>Điều tôi rút ra được là một phản hồi nhanh, dù ngắn gọn, vẫn tốt hơn là im lặng.</t>
         </is>
       </c>
-      <c r="E426" t="inlineStr">
+      <c r="E426" s="2" t="inlineStr">
         <is>
           <t>What I've learned is that a quick reply, even brief, is better than silence.</t>
         </is>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="E451" s="2" t="inlineStr">
         <is>
-          <t>We need to check references before making a decision.</t>
+          <t>We need to check references, before making a decision.</t>
         </is>
       </c>
       <c r="F451" s="2" t="inlineStr">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>We need to extend the offer before the end of this week.</t>
+          <t>We need to extend the offer, before the end of this week.</t>
         </is>
       </c>
       <c r="F454" s="2" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>We need to consider the risk if the candidate declines the offer.</t>
+          <t>We need to consider the risk, if the candidate declines the offer.</t>
         </is>
       </c>
       <c r="F463" s="2" t="inlineStr">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>The candidate is negotiating benefits before accepting the offer.</t>
+          <t>The candidate is negotiating benefits, before accepting the offer.</t>
         </is>
       </c>
       <c r="F465" s="2" t="inlineStr">
@@ -14411,7 +14411,7 @@
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>We need to decide quickly before the candidate accepts another offer.</t>
+          <t>We need to decide quickly, before the candidate accepts another offer.</t>
         </is>
       </c>
       <c r="F466" s="2" t="inlineStr">
@@ -14471,7 +14471,7 @@
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>I think we should close the deal before we lose the candidate to a competitor.</t>
+          <t>I think we should close the deal, before we lose the candidate to a competitor.</t>
         </is>
       </c>
       <c r="F468" s="2" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>We should have a quick chat after the interview.</t>
+          <t>We should have a quick chat, after the interview.</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>Can you confirm before we send the offer?</t>
+          <t>Can you confirm, before we send the offer?</t>
         </is>
       </c>
       <c r="F492" s="2" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>We should align before informing the candidate.</t>
+          <t>We should align, before informing the candidate.</t>
         </is>
       </c>
       <c r="F496" s="2" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>I need to discuss further with you before making the final decision.</t>
+          <t>I need to discuss further with you, before making the final decision.</t>
         </is>
       </c>
       <c r="F498" s="2" t="inlineStr">
@@ -15551,7 +15551,7 @@
       </c>
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>You need to decide before the candidate accepts another offer.</t>
+          <t>You need to decide, before the candidate accepts another offer.</t>
         </is>
       </c>
       <c r="F504" s="2" t="inlineStr">
@@ -15581,7 +15581,7 @@
       </c>
       <c r="E505" s="2" t="inlineStr">
         <is>
-          <t>We need alignment between HR and you before proceeding with the offer.</t>
+          <t>We need alignment between HR and you, before proceeding with the offer.</t>
         </is>
       </c>
       <c r="F505" s="2" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="E507" s="2" t="inlineStr">
         <is>
-          <t>Are you a bit hesitant because the candidate lacks industry experience in energy?</t>
+          <t>Are you a bit hesitant, because the candidate lacks industry experience in energy?</t>
         </is>
       </c>
       <c r="F507" s="2" t="inlineStr">
@@ -15701,7 +15701,7 @@
       </c>
       <c r="E509" s="2" t="inlineStr">
         <is>
-          <t>You should think twice before rejecting such a promising candidate.</t>
+          <t>You should think twice, before rejecting such a promising candidate.</t>
         </is>
       </c>
       <c r="F509" s="2" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="E517" s="2" t="inlineStr">
         <is>
-          <t>Honestly, it seems like you'd already made up your mind before the interview even ended.</t>
+          <t>Honestly, it seems like you'd already made up your mind, before the interview even ended.</t>
         </is>
       </c>
       <c r="F517" s="2" t="inlineStr">
@@ -16001,7 +16001,7 @@
       </c>
       <c r="E519" s="2" t="inlineStr">
         <is>
-          <t>I think you're hesitant because you're afraid of hiring wrong again.</t>
+          <t>I think you're hesitant, because you're afraid of hiring wrong again.</t>
         </is>
       </c>
       <c r="F519" s="2" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="E522" s="2" t="inlineStr">
         <is>
-          <t>Don't rush to blame HR if you haven't decided in time.</t>
+          <t>Don't rush to blame HR, if you haven't decided in time.</t>
         </is>
       </c>
       <c r="F522" s="2" t="inlineStr">
@@ -16571,7 +16571,7 @@
       </c>
       <c r="E538" s="2" t="inlineStr">
         <is>
-          <t>You need to complete the management training before being promoted.</t>
+          <t>You need to complete the management training, before being promoted.</t>
         </is>
       </c>
       <c r="F538" s="2" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="E558" s="2" t="inlineStr">
         <is>
-          <t>We need to weigh the retention risk if promotions aren't timely.</t>
+          <t>We need to weigh the retention risk, if promotions aren't timely.</t>
         </is>
       </c>
       <c r="F558" s="2" t="inlineStr">
@@ -17411,7 +17411,7 @@
       </c>
       <c r="E566" s="2" t="inlineStr">
         <is>
-          <t>There's a risk of losing motivation if an employee is denied promotion repeatedly.</t>
+          <t>There's a risk of losing motivation, if an employee is denied promotion repeatedly.</t>
         </is>
       </c>
       <c r="F566" s="2" t="inlineStr">
@@ -17561,7 +17561,7 @@
       </c>
       <c r="E571" s="2" t="inlineStr">
         <is>
-          <t>I think we should handle this tactfully before it turns into internal drama.</t>
+          <t>I think we should handle this tactfully, before it turns into internal drama.</t>
         </is>
       </c>
       <c r="F571" s="2" t="inlineStr">
@@ -18521,7 +18521,7 @@
       </c>
       <c r="E603" s="2" t="inlineStr">
         <is>
-          <t>We should revisit department KPIs when there are major staffing changes.</t>
+          <t>We should revisit department KPIs, when there are major staffing changes.</t>
         </is>
       </c>
       <c r="F603" s="2" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="E610" s="2" t="inlineStr">
         <is>
-          <t>We need to renegotiate department KPIs with heads before officially announcing the company KPI.</t>
+          <t>We need to renegotiate department KPIs with heads, before officially announcing the company KPI.</t>
         </is>
       </c>
       <c r="F610" s="2" t="inlineStr">
@@ -19211,7 +19211,7 @@
       </c>
       <c r="E626" s="2" t="inlineStr">
         <is>
-          <t>In the end, KPIs only matter if they keep the organization moving in the right direction.</t>
+          <t>In the end, KPIs only matter, if they keep the organization moving in the right direction.</t>
         </is>
       </c>
       <c r="F626" s="2" t="inlineStr">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="E657" s="2" t="inlineStr">
         <is>
-          <t>We're gradually losing our competitive edge if we don't act early to retain key talent.</t>
+          <t>We're gradually losing our competitive edge, if we don't act early to retain key talent.</t>
         </is>
       </c>
       <c r="F657" s="2" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="E662" s="2" t="inlineStr">
         <is>
-          <t>There's a view that the company should proactively offer a promotion path before employees have to ask.</t>
+          <t>There's a view that the company should proactively offer a promotion path, before employees have to ask.</t>
         </is>
       </c>
       <c r="F662" s="2" t="inlineStr">
@@ -20621,7 +20621,7 @@
       </c>
       <c r="E673" s="2" t="inlineStr">
         <is>
-          <t>Don't be surprised when your best employee is the first to leave if they feel overlooked.</t>
+          <t>Don't be surprised, when your best employee is the first to leave, if they feel overlooked.</t>
         </is>
       </c>
       <c r="F673" s="2" t="inlineStr">
@@ -21221,7 +21221,7 @@
       </c>
       <c r="E693" s="2" t="inlineStr">
         <is>
-          <t>There's legal risk if the policy doesn't align with current law.</t>
+          <t>There's legal risk, if the policy doesn't align with current law.</t>
         </is>
       </c>
       <c r="F693" s="2" t="inlineStr">
@@ -21371,7 +21371,7 @@
       </c>
       <c r="E698" s="2" t="inlineStr">
         <is>
-          <t>We need to prepare all compliance documents before the audit.</t>
+          <t>We need to prepare all compliance documents, before the audit.</t>
         </is>
       </c>
       <c r="F698" s="2" t="inlineStr">
@@ -21701,7 +21701,7 @@
       </c>
       <c r="E709" s="2" t="inlineStr">
         <is>
-          <t>There's a possibility the company will be fined if this isn't remedied in time.</t>
+          <t>There's a possibility the company will be fined, if this isn't remedied in time.</t>
         </is>
       </c>
       <c r="F709" s="2" t="inlineStr">
@@ -21881,7 +21881,7 @@
       </c>
       <c r="E715" s="2" t="inlineStr">
         <is>
-          <t>We need to assess security risk when sharing HR data between the two countries.</t>
+          <t>We need to assess security risk, when sharing HR data between the two countries.</t>
         </is>
       </c>
       <c r="F715" s="2" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="E721" s="2" t="inlineStr">
         <is>
-          <t>This needs to be handled discreetly before it spreads.</t>
+          <t>This needs to be handled discreetly, before it spreads.</t>
         </is>
       </c>
       <c r="F721" s="2" t="inlineStr">
@@ -22181,7 +22181,7 @@
       </c>
       <c r="E725" s="2" t="inlineStr">
         <is>
-          <t>Don't wait for a data leak to happen before thinking about security.</t>
+          <t>Don't wait for a data leak to happen, before thinking about security.</t>
         </is>
       </c>
       <c r="F725" s="2" t="inlineStr">
@@ -23201,7 +23201,7 @@
       </c>
       <c r="E759" s="2" t="inlineStr">
         <is>
-          <t>There's a risk of losing top talent if workload overload isn't addressed.</t>
+          <t>There's a risk of losing top talent, if workload overload isn't addressed.</t>
         </is>
       </c>
       <c r="F759" s="2" t="inlineStr">
@@ -23891,7 +23891,7 @@
       </c>
       <c r="E782" s="2" t="inlineStr">
         <is>
-          <t>This benefit applies after two months of probation.</t>
+          <t>This benefit applies, after two months of probation.</t>
         </is>
       </c>
       <c r="F782" s="2" t="inlineStr">
@@ -24431,7 +24431,7 @@
       </c>
       <c r="E800" s="2" t="inlineStr">
         <is>
-          <t>Expanding benefits needs board approval before the end of the quarter.</t>
+          <t>Expanding benefits needs board approval, before the end of the quarter.</t>
         </is>
       </c>
       <c r="F800" s="2" t="inlineStr">
@@ -24671,7 +24671,7 @@
       </c>
       <c r="E808" s="2" t="inlineStr">
         <is>
-          <t>There's a risk of losing competitive advantage if the benefits package isn't improved in time.</t>
+          <t>There's a risk of losing competitive advantage, if the benefits package isn't improved in time.</t>
         </is>
       </c>
       <c r="F808" s="2" t="inlineStr">
@@ -25031,7 +25031,7 @@
       </c>
       <c r="E820" s="2" t="inlineStr">
         <is>
-          <t>She chose to stay because of the thoughtful family-care benefits.</t>
+          <t>She chose to stay, because of the thoughtful family-care benefits.</t>
         </is>
       </c>
       <c r="F820" s="2" t="inlineStr">
@@ -25421,7 +25421,7 @@
       </c>
       <c r="E833" s="2" t="inlineStr">
         <is>
-          <t>We refer to market salary rates before making an offer.</t>
+          <t>We refer to market salary rates, before making an offer.</t>
         </is>
       </c>
       <c r="F833" s="2" t="inlineStr">
@@ -25571,7 +25571,7 @@
       </c>
       <c r="E838" s="2" t="inlineStr">
         <is>
-          <t>We need to survey market salaries before adjusting the salary guide.</t>
+          <t>We need to survey market salaries, before adjusting the salary guide.</t>
         </is>
       </c>
       <c r="F838" s="2" t="inlineStr">
@@ -25661,7 +25661,7 @@
       </c>
       <c r="E841" s="2" t="inlineStr">
         <is>
-          <t>The starting salary will be adjusted after six months of probation.</t>
+          <t>The starting salary will be adjusted, after six months of probation.</t>
         </is>
       </c>
       <c r="F841" s="2" t="inlineStr">
@@ -26051,7 +26051,7 @@
       </c>
       <c r="E854" s="2" t="inlineStr">
         <is>
-          <t>Salary adjustments need approval before being announced to employees.</t>
+          <t>Salary adjustments need approval, before being announced to employees.</t>
         </is>
       </c>
       <c r="F854" s="2" t="inlineStr">
@@ -26171,7 +26171,7 @@
       </c>
       <c r="E858" s="2" t="inlineStr">
         <is>
-          <t>There's a risk of losing top talent if the salary guide isn't adjusted in line with the market in time.</t>
+          <t>There's a risk of losing top talent, if the salary guide isn't adjusted in line with the market in time.</t>
         </is>
       </c>
       <c r="F858" s="2" t="inlineStr">
@@ -26411,7 +26411,7 @@
       </c>
       <c r="E866" s="2" t="inlineStr">
         <is>
-          <t>There's a risk of losing candidates if the initial offer is too far below market expectations.</t>
+          <t>There's a risk of losing candidates, if the initial offer is too far below market expectations.</t>
         </is>
       </c>
       <c r="F866" s="2" t="inlineStr">
@@ -26531,7 +26531,7 @@
       </c>
       <c r="E870" s="2" t="inlineStr">
         <is>
-          <t>She decided to stay because she felt fairly paid for her effort.</t>
+          <t>She decided to stay, because she felt fairly paid for her effort.</t>
         </is>
       </c>
       <c r="F870" s="2" t="inlineStr">
@@ -27581,7 +27581,7 @@
       </c>
       <c r="E905" s="2" t="inlineStr">
         <is>
-          <t>He tends to perform better when given autonomy.</t>
+          <t>He tends to perform better, when given autonomy.</t>
         </is>
       </c>
       <c r="F905" s="2" t="inlineStr">
@@ -27821,7 +27821,7 @@
       </c>
       <c r="E913" s="2" t="inlineStr">
         <is>
-          <t>She needs to improve emotional control when working under high pressure.</t>
+          <t>She needs to improve emotional control, when working under high pressure.</t>
         </is>
       </c>
       <c r="F913" s="2" t="inlineStr">
@@ -28091,7 +28091,7 @@
       </c>
       <c r="E922" s="2" t="inlineStr">
         <is>
-          <t>She's exactly the person you want on your team when things fall apart.</t>
+          <t>She's exactly the person you want on your team, when things fall apart.</t>
         </is>
       </c>
       <c r="F922" s="2" t="inlineStr">
@@ -28211,7 +28211,7 @@
       </c>
       <c r="E926" s="2" t="inlineStr">
         <is>
-          <t>She's the kind of person who calms the whole room when things get chaotic.</t>
+          <t>She's the kind of person who calms the whole room, when things get chaotic.</t>
         </is>
       </c>
       <c r="F926" s="2" t="inlineStr">
@@ -28751,7 +28751,7 @@
       </c>
       <c r="E944" s="2" t="inlineStr">
         <is>
-          <t>We need to update the org chart after this recruitment round.</t>
+          <t>We need to update the org chart, after this recruitment round.</t>
         </is>
       </c>
       <c r="F944" s="2" t="inlineStr">
@@ -29321,7 +29321,7 @@
       </c>
       <c r="E963" s="2" t="inlineStr">
         <is>
-          <t>We need a clear transition roadmap before announcing the new org chart.</t>
+          <t>We need a clear transition roadmap, before announcing the new org chart.</t>
         </is>
       </c>
       <c r="F963" s="2" t="inlineStr">
@@ -29471,7 +29471,7 @@
       </c>
       <c r="E968" s="2" t="inlineStr">
         <is>
-          <t>Don't be surprised if this structure changes again next year.</t>
+          <t>Don't be surprised, if this structure changes again next year.</t>
         </is>
       </c>
       <c r="F968" s="2" t="inlineStr">
@@ -30791,7 +30791,7 @@
       </c>
       <c r="E1012" s="2" t="inlineStr">
         <is>
-          <t>We need to assess operational risk before officially changing the organizational model.</t>
+          <t>We need to assess operational risk, before officially changing the organizational model.</t>
         </is>
       </c>
       <c r="F1012" s="2" t="inlineStr">
@@ -30911,7 +30911,7 @@
       </c>
       <c r="E1016" s="2" t="inlineStr">
         <is>
-          <t>There's a view that the company should consolidate current markets before expanding further.</t>
+          <t>There's a view that the company should consolidate current markets, before expanding further.</t>
         </is>
       </c>
       <c r="F1016" s="2" t="inlineStr">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="E1022" s="2" t="inlineStr">
         <is>
-          <t>We need to build a solid foundation before thinking about expanding further.</t>
+          <t>We need to build a solid foundation, before thinking about expanding further.</t>
         </is>
       </c>
       <c r="F1022" s="2" t="inlineStr">
@@ -31151,7 +31151,7 @@
       </c>
       <c r="E1024" s="2" t="inlineStr">
         <is>
-          <t>A long-term vision needs a lean enough machine to pivot quickly when the market shifts.</t>
+          <t>A long-term vision needs a lean enough machine to pivot quickly, when the market shifts.</t>
         </is>
       </c>
       <c r="F1024" s="2" t="inlineStr">
@@ -32081,7 +32081,7 @@
       </c>
       <c r="E1055" s="2" t="inlineStr">
         <is>
-          <t>We need to measure how well knowledge is applied after each training course.</t>
+          <t>We need to measure how well knowledge is applied, after each training course.</t>
         </is>
       </c>
       <c r="F1055" s="2" t="inlineStr">
@@ -32261,7 +32261,7 @@
       </c>
       <c r="E1061" s="2" t="inlineStr">
         <is>
-          <t>We need to measure the ROI of training programs before continuing to invest.</t>
+          <t>We need to measure the ROI of training programs, before continuing to invest.</t>
         </is>
       </c>
       <c r="F1061" s="2" t="inlineStr">
@@ -32681,7 +32681,7 @@
       </c>
       <c r="E1075" s="2" t="inlineStr">
         <is>
-          <t>Training doesn't end when the course ends, it's just the beginning.</t>
+          <t>Training doesn't end, when the course ends, it's just the beginning.</t>
         </is>
       </c>
       <c r="F1075" s="2" t="inlineStr">
